--- a/public/templates/NXP-038_Container_Import_Template.xlsx
+++ b/public/templates/NXP-038_Container_Import_Template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HuongDan" sheetId="1" r:id="Recf48dd6f22a4aaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cang_Tau" sheetId="2" r:id="Rbea6b5524eff4b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CongTyVanChuyen" sheetId="3" r:id="R06842bae72d54788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HuongDan" sheetId="1" r:id="Rebfec7c5a2e74785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cang_Tau" sheetId="2" r:id="R768d4baac7af4195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CongTyVanChuyen" sheetId="3" r:id="R46cb039dc92c4f1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -68,6 +68,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF334155"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -167,7 +172,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -259,6 +264,11 @@
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -267,8 +277,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PortContainerImport" displayName="PortContainerImport" ref="A1:M200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CangTauImportTable" displayName="CangTauImportTable" ref="A1:J7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
     <x:tableColumn id="1" name="container_number"/>
     <x:tableColumn id="2" name="container_type"/>
     <x:tableColumn id="3" name="source_reference"/>
@@ -276,12 +286,9 @@
     <x:tableColumn id="5" name="load_status"/>
     <x:tableColumn id="6" name="cargo_type"/>
     <x:tableColumn id="7" name="gross_weight_kg"/>
-    <x:tableColumn id="8" name="vessel_call_code"/>
-    <x:tableColumn id="9" name="expected_arrival_at"/>
-    <x:tableColumn id="10" name="expected_available_at"/>
-    <x:tableColumn id="11" name="bl_booking_number"/>
-    <x:tableColumn id="12" name="customer_name"/>
-    <x:tableColumn id="13" name="transport_company_name"/>
+    <x:tableColumn id="8" name="expected_arrival_at"/>
+    <x:tableColumn id="9" name="bl_booking_number"/>
+    <x:tableColumn id="10" name="customer_name"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -530,7 +537,7 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="27" t="str">
-        <x:v>Chọn đúng sheet theo nguồn dữ liệu. Không đổi tên cột ở hàng 1. Ngày dùng YYYY-MM-DD; ngày giờ dùng YYYY-MM-DD HH:mm.</x:v>
+        <x:v>Chọn đúng sheet theo nguồn dữ liệu. Không đổi tên cột ở hàng 1. Ngày dùng YYYY-MM-DD; ngày giờ dùng YYYY-MM-DD HH:mm. Nguồn cảng chỉ nhập ETA; hệ thống tạm tính thời gian hoàn tất bốc dỡ bằng ETA + 12 giờ.</x:v>
       </x:c>
       <x:c r="B3" s="28"/>
       <x:c r="C3" s="28"/>
@@ -566,7 +573,7 @@
         <x:v>Ghi chú</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="29" t="str">
         <x:v>Cang_Tau</x:v>
       </x:c>
@@ -583,7 +590,7 @@
         <x:v>1.000 dòng / 5 MB</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Tạo Container Master nếu chưa có và lượt dỡ tàu dự kiến.</x:v>
+        <x:v>Tạo Container Master và lượt dỡ tàu dự kiến. Không nhập mã chuyến tàu, thời gian sẵn sàng hoặc đơn vị vận chuyển ở giai đoạn này.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -713,59 +720,53 @@
   <x:cols>
     <x:col min="1" max="1" width="17.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="19" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="43" t="str">
         <x:v>container_number</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="43" t="str">
         <x:v>container_type</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="43" t="str">
         <x:v>source_reference</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="43" t="str">
         <x:v>seal_number</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="E1" s="43" t="str">
         <x:v>load_status</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="F1" s="43" t="str">
         <x:v>cargo_type</x:v>
       </x:c>
-      <x:c r="G1" s="8" t="str">
+      <x:c r="G1" s="43" t="str">
         <x:v>gross_weight_kg</x:v>
       </x:c>
-      <x:c r="H1" s="8" t="str">
-        <x:v>vessel_call_code</x:v>
-      </x:c>
-      <x:c r="I1" s="8" t="str">
+      <x:c r="H1" s="43" t="str">
         <x:v>expected_arrival_at</x:v>
       </x:c>
-      <x:c r="J1" s="8" t="str">
-        <x:v>expected_available_at</x:v>
-      </x:c>
-      <x:c r="K1" s="8" t="str">
+      <x:c r="I1" s="43" t="str">
         <x:v>bl_booking_number</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="J1" s="43" t="str">
         <x:v>customer_name</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
-        <x:v>transport_company_name</x:v>
-      </x:c>
+      <x:c r="K1" s="8"/>
+      <x:c r="L1" s="8"/>
+      <x:c r="M1" s="8"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -789,94 +790,190 @@
       <x:c r="G2" s="39" t="n">
         <x:v>26493</x:v>
       </x:c>
-      <x:c r="H2" s="9" t="str"/>
-      <x:c r="I2" s="35" t="n">
+      <x:c r="H2" s="35" t="n">
         <x:v>46114.70763888889</x:v>
       </x:c>
-      <x:c r="J2" s="35" t="n">
-        <x:v>46115.33333333333</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
+      <x:c r="I2" s="35" t="str">
         <x:v>238600081908</x:v>
       </x:c>
-      <x:c r="L2" s="9" t="str">
+      <x:c r="J2" s="35" t="str">
         <x:v>CÔNG TY TNHH MTV SẢN XUẤT KỆ KHO HÀNG BHD VIỆT NAM</x:v>
       </x:c>
-      <x:c r="M2" s="9" t="str">
-        <x:v>CÔNG TY TNHH MTV SẢN XUẤT KỆ KHO HÀNG BHD VIỆT NAM</x:v>
-      </x:c>
+      <x:c r="K2" s="9"/>
+      <x:c r="L2" s="9"/>
+      <x:c r="M2" s="9"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="10"/>
-      <x:c r="B3" s="10"/>
-      <x:c r="C3" s="10"/>
-      <x:c r="D3" s="10"/>
-      <x:c r="E3" s="10"/>
-      <x:c r="F3" s="10"/>
-      <x:c r="G3" s="40"/>
-      <x:c r="H3" s="10"/>
-      <x:c r="I3" s="36"/>
-      <x:c r="J3" s="36"/>
+      <x:c r="A3" s="10" t="str">
+        <x:v>EMCU8361795</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>260317SP545549</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>A1795572</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="G3" s="40" t="n">
+        <x:v>28300</x:v>
+      </x:c>
+      <x:c r="H3" s="36" t="n">
+        <x:v>46082.256944444445</x:v>
+      </x:c>
+      <x:c r="I3" s="36" t="str">
+        <x:v>400500499060</x:v>
+      </x:c>
+      <x:c r="J3" s="36" t="str">
+        <x:v>SHINING INTERNATIONAL DEVELOPMENT LIMITED</x:v>
+      </x:c>
       <x:c r="K3" s="10"/>
       <x:c r="L3" s="10"/>
       <x:c r="M3" s="10"/>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="10"/>
-      <x:c r="B4" s="10"/>
-      <x:c r="C4" s="10"/>
-      <x:c r="D4" s="10"/>
-      <x:c r="E4" s="10"/>
-      <x:c r="F4" s="10"/>
-      <x:c r="G4" s="40"/>
-      <x:c r="H4" s="10"/>
-      <x:c r="I4" s="36"/>
-      <x:c r="J4" s="36"/>
+      <x:c r="A4" s="10" t="str">
+        <x:v>ONEU7524599</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>260331PA558185</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>VN83568AQ</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="G4" s="40" t="n">
+        <x:v>26000</x:v>
+      </x:c>
+      <x:c r="H4" s="36" t="n">
+        <x:v>46115.41736111111</x:v>
+      </x:c>
+      <x:c r="I4" s="36" t="str">
+        <x:v>DADG02202800</x:v>
+      </x:c>
+      <x:c r="J4" s="36" t="str">
+        <x:v>CÔNG TY CỔ PHẦN VANTAGE LOGISTICS</x:v>
+      </x:c>
       <x:c r="K4" s="10"/>
       <x:c r="L4" s="10"/>
       <x:c r="M4" s="10"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="10"/>
-      <x:c r="B5" s="10"/>
-      <x:c r="C5" s="10"/>
-      <x:c r="D5" s="10"/>
-      <x:c r="E5" s="10"/>
-      <x:c r="F5" s="10"/>
-      <x:c r="G5" s="40"/>
-      <x:c r="H5" s="10"/>
-      <x:c r="I5" s="36"/>
-      <x:c r="J5" s="36"/>
+      <x:c r="A5" s="10" t="str">
+        <x:v>ONEU7524599</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>260301PA531586</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>VN83063AQ</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="G5" s="40" t="n">
+        <x:v>32500</x:v>
+      </x:c>
+      <x:c r="H5" s="36" t="n">
+        <x:v>46084.24513888889</x:v>
+      </x:c>
+      <x:c r="I5" s="36" t="str">
+        <x:v>DADG02482400</x:v>
+      </x:c>
+      <x:c r="J5" s="36" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
       <x:c r="K5" s="10"/>
       <x:c r="L5" s="10"/>
       <x:c r="M5" s="10"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="10"/>
-      <x:c r="B6" s="10"/>
-      <x:c r="C6" s="10"/>
-      <x:c r="D6" s="10"/>
-      <x:c r="E6" s="10"/>
-      <x:c r="F6" s="10"/>
-      <x:c r="G6" s="40"/>
-      <x:c r="H6" s="10"/>
-      <x:c r="I6" s="36"/>
-      <x:c r="J6" s="36"/>
+      <x:c r="A6" s="10" t="str">
+        <x:v>GCXU5261606</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>260331PA558329</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>VN83572AQ</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="G6" s="40" t="n">
+        <x:v>9496</x:v>
+      </x:c>
+      <x:c r="H6" s="36" t="n">
+        <x:v>46118.447222222225</x:v>
+      </x:c>
+      <x:c r="I6" s="36" t="str">
+        <x:v>DADG02410900</x:v>
+      </x:c>
+      <x:c r="J6" s="36" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẠI LÝ VẬN TẢI SAFI TẠI ĐÀ NẴNG</x:v>
+      </x:c>
       <x:c r="K6" s="10"/>
       <x:c r="L6" s="10"/>
       <x:c r="M6" s="10"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="10"/>
-      <x:c r="B7" s="10"/>
-      <x:c r="C7" s="10"/>
-      <x:c r="D7" s="10"/>
-      <x:c r="E7" s="10"/>
-      <x:c r="F7" s="10"/>
-      <x:c r="G7" s="40"/>
-      <x:c r="H7" s="10"/>
-      <x:c r="I7" s="36"/>
-      <x:c r="J7" s="36"/>
+      <x:c r="A7" s="10" t="str">
+        <x:v>GCXU5261606</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>260301PA531586</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>VN83064AQ</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="G7" s="40" t="n">
+        <x:v>32500</x:v>
+      </x:c>
+      <x:c r="H7" s="36" t="n">
+        <x:v>46084.24513888889</x:v>
+      </x:c>
+      <x:c r="I7" s="36" t="str">
+        <x:v>DADG02482400</x:v>
+      </x:c>
+      <x:c r="J7" s="36" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
       <x:c r="K7" s="10"/>
       <x:c r="L7" s="10"/>
       <x:c r="M7" s="10"/>
@@ -889,7 +986,7 @@
       <x:c r="E8" s="10"/>
       <x:c r="F8" s="10"/>
       <x:c r="G8" s="40"/>
-      <x:c r="H8" s="10"/>
+      <x:c r="H8" s="36"/>
       <x:c r="I8" s="36"/>
       <x:c r="J8" s="36"/>
       <x:c r="K8" s="10"/>
@@ -904,7 +1001,7 @@
       <x:c r="E9" s="10"/>
       <x:c r="F9" s="10"/>
       <x:c r="G9" s="40"/>
-      <x:c r="H9" s="10"/>
+      <x:c r="H9" s="36"/>
       <x:c r="I9" s="36"/>
       <x:c r="J9" s="36"/>
       <x:c r="K9" s="10"/>
@@ -919,7 +1016,7 @@
       <x:c r="E10" s="10"/>
       <x:c r="F10" s="10"/>
       <x:c r="G10" s="40"/>
-      <x:c r="H10" s="10"/>
+      <x:c r="H10" s="36"/>
       <x:c r="I10" s="36"/>
       <x:c r="J10" s="36"/>
       <x:c r="K10" s="10"/>
@@ -934,7 +1031,7 @@
       <x:c r="E11" s="10"/>
       <x:c r="F11" s="10"/>
       <x:c r="G11" s="40"/>
-      <x:c r="H11" s="10"/>
+      <x:c r="H11" s="36"/>
       <x:c r="I11" s="36"/>
       <x:c r="J11" s="36"/>
       <x:c r="K11" s="10"/>
@@ -949,7 +1046,7 @@
       <x:c r="E12" s="10"/>
       <x:c r="F12" s="10"/>
       <x:c r="G12" s="40"/>
-      <x:c r="H12" s="10"/>
+      <x:c r="H12" s="36"/>
       <x:c r="I12" s="36"/>
       <x:c r="J12" s="36"/>
       <x:c r="K12" s="10"/>
@@ -964,7 +1061,7 @@
       <x:c r="E13" s="10"/>
       <x:c r="F13" s="10"/>
       <x:c r="G13" s="40"/>
-      <x:c r="H13" s="10"/>
+      <x:c r="H13" s="36"/>
       <x:c r="I13" s="36"/>
       <x:c r="J13" s="36"/>
       <x:c r="K13" s="10"/>
@@ -979,7 +1076,7 @@
       <x:c r="E14" s="10"/>
       <x:c r="F14" s="10"/>
       <x:c r="G14" s="40"/>
-      <x:c r="H14" s="10"/>
+      <x:c r="H14" s="36"/>
       <x:c r="I14" s="36"/>
       <x:c r="J14" s="36"/>
       <x:c r="K14" s="10"/>
@@ -994,7 +1091,7 @@
       <x:c r="E15" s="10"/>
       <x:c r="F15" s="10"/>
       <x:c r="G15" s="40"/>
-      <x:c r="H15" s="10"/>
+      <x:c r="H15" s="36"/>
       <x:c r="I15" s="36"/>
       <x:c r="J15" s="36"/>
       <x:c r="K15" s="10"/>
@@ -1009,7 +1106,7 @@
       <x:c r="E16" s="10"/>
       <x:c r="F16" s="10"/>
       <x:c r="G16" s="40"/>
-      <x:c r="H16" s="10"/>
+      <x:c r="H16" s="36"/>
       <x:c r="I16" s="36"/>
       <x:c r="J16" s="36"/>
       <x:c r="K16" s="10"/>
@@ -1024,7 +1121,7 @@
       <x:c r="E17" s="10"/>
       <x:c r="F17" s="10"/>
       <x:c r="G17" s="40"/>
-      <x:c r="H17" s="10"/>
+      <x:c r="H17" s="36"/>
       <x:c r="I17" s="36"/>
       <x:c r="J17" s="36"/>
       <x:c r="K17" s="10"/>
@@ -1039,7 +1136,7 @@
       <x:c r="E18" s="10"/>
       <x:c r="F18" s="10"/>
       <x:c r="G18" s="40"/>
-      <x:c r="H18" s="10"/>
+      <x:c r="H18" s="36"/>
       <x:c r="I18" s="36"/>
       <x:c r="J18" s="36"/>
       <x:c r="K18" s="10"/>
@@ -1054,7 +1151,7 @@
       <x:c r="E19" s="10"/>
       <x:c r="F19" s="10"/>
       <x:c r="G19" s="40"/>
-      <x:c r="H19" s="10"/>
+      <x:c r="H19" s="36"/>
       <x:c r="I19" s="36"/>
       <x:c r="J19" s="36"/>
       <x:c r="K19" s="10"/>
@@ -1069,7 +1166,7 @@
       <x:c r="E20" s="10"/>
       <x:c r="F20" s="10"/>
       <x:c r="G20" s="40"/>
-      <x:c r="H20" s="10"/>
+      <x:c r="H20" s="36"/>
       <x:c r="I20" s="36"/>
       <x:c r="J20" s="36"/>
       <x:c r="K20" s="10"/>
@@ -1084,7 +1181,7 @@
       <x:c r="E21" s="10"/>
       <x:c r="F21" s="10"/>
       <x:c r="G21" s="40"/>
-      <x:c r="H21" s="10"/>
+      <x:c r="H21" s="36"/>
       <x:c r="I21" s="36"/>
       <x:c r="J21" s="36"/>
       <x:c r="K21" s="10"/>
@@ -1099,7 +1196,7 @@
       <x:c r="E22" s="10"/>
       <x:c r="F22" s="10"/>
       <x:c r="G22" s="40"/>
-      <x:c r="H22" s="10"/>
+      <x:c r="H22" s="36"/>
       <x:c r="I22" s="36"/>
       <x:c r="J22" s="36"/>
       <x:c r="K22" s="10"/>
@@ -1114,7 +1211,7 @@
       <x:c r="E23" s="10"/>
       <x:c r="F23" s="10"/>
       <x:c r="G23" s="40"/>
-      <x:c r="H23" s="10"/>
+      <x:c r="H23" s="36"/>
       <x:c r="I23" s="36"/>
       <x:c r="J23" s="36"/>
       <x:c r="K23" s="10"/>
@@ -1129,7 +1226,7 @@
       <x:c r="E24" s="10"/>
       <x:c r="F24" s="10"/>
       <x:c r="G24" s="40"/>
-      <x:c r="H24" s="10"/>
+      <x:c r="H24" s="36"/>
       <x:c r="I24" s="36"/>
       <x:c r="J24" s="36"/>
       <x:c r="K24" s="10"/>
@@ -1144,7 +1241,7 @@
       <x:c r="E25" s="10"/>
       <x:c r="F25" s="10"/>
       <x:c r="G25" s="40"/>
-      <x:c r="H25" s="10"/>
+      <x:c r="H25" s="36"/>
       <x:c r="I25" s="36"/>
       <x:c r="J25" s="36"/>
       <x:c r="K25" s="10"/>
@@ -1159,7 +1256,7 @@
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="40"/>
-      <x:c r="H26" s="10"/>
+      <x:c r="H26" s="36"/>
       <x:c r="I26" s="36"/>
       <x:c r="J26" s="36"/>
       <x:c r="K26" s="10"/>
@@ -1174,7 +1271,7 @@
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="40"/>
-      <x:c r="H27" s="10"/>
+      <x:c r="H27" s="36"/>
       <x:c r="I27" s="36"/>
       <x:c r="J27" s="36"/>
       <x:c r="K27" s="10"/>
@@ -1189,7 +1286,7 @@
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="40"/>
-      <x:c r="H28" s="10"/>
+      <x:c r="H28" s="36"/>
       <x:c r="I28" s="36"/>
       <x:c r="J28" s="36"/>
       <x:c r="K28" s="10"/>
@@ -1204,7 +1301,7 @@
       <x:c r="E29" s="10"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="40"/>
-      <x:c r="H29" s="10"/>
+      <x:c r="H29" s="36"/>
       <x:c r="I29" s="36"/>
       <x:c r="J29" s="36"/>
       <x:c r="K29" s="10"/>
@@ -1219,7 +1316,7 @@
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="40"/>
-      <x:c r="H30" s="10"/>
+      <x:c r="H30" s="36"/>
       <x:c r="I30" s="36"/>
       <x:c r="J30" s="36"/>
       <x:c r="K30" s="10"/>
@@ -1234,7 +1331,7 @@
       <x:c r="E31" s="10"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="40"/>
-      <x:c r="H31" s="10"/>
+      <x:c r="H31" s="36"/>
       <x:c r="I31" s="36"/>
       <x:c r="J31" s="36"/>
       <x:c r="K31" s="10"/>
@@ -1249,7 +1346,7 @@
       <x:c r="E32" s="10"/>
       <x:c r="F32" s="10"/>
       <x:c r="G32" s="40"/>
-      <x:c r="H32" s="10"/>
+      <x:c r="H32" s="36"/>
       <x:c r="I32" s="36"/>
       <x:c r="J32" s="36"/>
       <x:c r="K32" s="10"/>
@@ -1264,7 +1361,7 @@
       <x:c r="E33" s="10"/>
       <x:c r="F33" s="10"/>
       <x:c r="G33" s="40"/>
-      <x:c r="H33" s="10"/>
+      <x:c r="H33" s="36"/>
       <x:c r="I33" s="36"/>
       <x:c r="J33" s="36"/>
       <x:c r="K33" s="10"/>
@@ -1279,7 +1376,7 @@
       <x:c r="E34" s="10"/>
       <x:c r="F34" s="10"/>
       <x:c r="G34" s="40"/>
-      <x:c r="H34" s="10"/>
+      <x:c r="H34" s="36"/>
       <x:c r="I34" s="36"/>
       <x:c r="J34" s="36"/>
       <x:c r="K34" s="10"/>
@@ -1294,7 +1391,7 @@
       <x:c r="E35" s="10"/>
       <x:c r="F35" s="10"/>
       <x:c r="G35" s="40"/>
-      <x:c r="H35" s="10"/>
+      <x:c r="H35" s="36"/>
       <x:c r="I35" s="36"/>
       <x:c r="J35" s="36"/>
       <x:c r="K35" s="10"/>
@@ -1309,7 +1406,7 @@
       <x:c r="E36" s="10"/>
       <x:c r="F36" s="10"/>
       <x:c r="G36" s="40"/>
-      <x:c r="H36" s="10"/>
+      <x:c r="H36" s="36"/>
       <x:c r="I36" s="36"/>
       <x:c r="J36" s="36"/>
       <x:c r="K36" s="10"/>
@@ -1324,7 +1421,7 @@
       <x:c r="E37" s="10"/>
       <x:c r="F37" s="10"/>
       <x:c r="G37" s="40"/>
-      <x:c r="H37" s="10"/>
+      <x:c r="H37" s="36"/>
       <x:c r="I37" s="36"/>
       <x:c r="J37" s="36"/>
       <x:c r="K37" s="10"/>
@@ -1339,7 +1436,7 @@
       <x:c r="E38" s="10"/>
       <x:c r="F38" s="10"/>
       <x:c r="G38" s="40"/>
-      <x:c r="H38" s="10"/>
+      <x:c r="H38" s="36"/>
       <x:c r="I38" s="36"/>
       <x:c r="J38" s="36"/>
       <x:c r="K38" s="10"/>
@@ -1354,7 +1451,7 @@
       <x:c r="E39" s="10"/>
       <x:c r="F39" s="10"/>
       <x:c r="G39" s="40"/>
-      <x:c r="H39" s="10"/>
+      <x:c r="H39" s="36"/>
       <x:c r="I39" s="36"/>
       <x:c r="J39" s="36"/>
       <x:c r="K39" s="10"/>
@@ -1369,7 +1466,7 @@
       <x:c r="E40" s="10"/>
       <x:c r="F40" s="10"/>
       <x:c r="G40" s="40"/>
-      <x:c r="H40" s="10"/>
+      <x:c r="H40" s="36"/>
       <x:c r="I40" s="36"/>
       <x:c r="J40" s="36"/>
       <x:c r="K40" s="10"/>
@@ -1384,7 +1481,7 @@
       <x:c r="E41" s="10"/>
       <x:c r="F41" s="10"/>
       <x:c r="G41" s="40"/>
-      <x:c r="H41" s="10"/>
+      <x:c r="H41" s="36"/>
       <x:c r="I41" s="36"/>
       <x:c r="J41" s="36"/>
       <x:c r="K41" s="10"/>
@@ -1399,7 +1496,7 @@
       <x:c r="E42" s="10"/>
       <x:c r="F42" s="10"/>
       <x:c r="G42" s="40"/>
-      <x:c r="H42" s="10"/>
+      <x:c r="H42" s="36"/>
       <x:c r="I42" s="36"/>
       <x:c r="J42" s="36"/>
       <x:c r="K42" s="10"/>
@@ -1414,7 +1511,7 @@
       <x:c r="E43" s="10"/>
       <x:c r="F43" s="10"/>
       <x:c r="G43" s="40"/>
-      <x:c r="H43" s="10"/>
+      <x:c r="H43" s="36"/>
       <x:c r="I43" s="36"/>
       <x:c r="J43" s="36"/>
       <x:c r="K43" s="10"/>
@@ -1429,7 +1526,7 @@
       <x:c r="E44" s="10"/>
       <x:c r="F44" s="10"/>
       <x:c r="G44" s="40"/>
-      <x:c r="H44" s="10"/>
+      <x:c r="H44" s="36"/>
       <x:c r="I44" s="36"/>
       <x:c r="J44" s="36"/>
       <x:c r="K44" s="10"/>
@@ -1444,7 +1541,7 @@
       <x:c r="E45" s="10"/>
       <x:c r="F45" s="10"/>
       <x:c r="G45" s="40"/>
-      <x:c r="H45" s="10"/>
+      <x:c r="H45" s="36"/>
       <x:c r="I45" s="36"/>
       <x:c r="J45" s="36"/>
       <x:c r="K45" s="10"/>
@@ -1459,7 +1556,7 @@
       <x:c r="E46" s="10"/>
       <x:c r="F46" s="10"/>
       <x:c r="G46" s="40"/>
-      <x:c r="H46" s="10"/>
+      <x:c r="H46" s="36"/>
       <x:c r="I46" s="36"/>
       <x:c r="J46" s="36"/>
       <x:c r="K46" s="10"/>
@@ -1474,7 +1571,7 @@
       <x:c r="E47" s="10"/>
       <x:c r="F47" s="10"/>
       <x:c r="G47" s="40"/>
-      <x:c r="H47" s="10"/>
+      <x:c r="H47" s="36"/>
       <x:c r="I47" s="36"/>
       <x:c r="J47" s="36"/>
       <x:c r="K47" s="10"/>
@@ -1489,7 +1586,7 @@
       <x:c r="E48" s="10"/>
       <x:c r="F48" s="10"/>
       <x:c r="G48" s="40"/>
-      <x:c r="H48" s="10"/>
+      <x:c r="H48" s="36"/>
       <x:c r="I48" s="36"/>
       <x:c r="J48" s="36"/>
       <x:c r="K48" s="10"/>
@@ -1504,7 +1601,7 @@
       <x:c r="E49" s="10"/>
       <x:c r="F49" s="10"/>
       <x:c r="G49" s="40"/>
-      <x:c r="H49" s="10"/>
+      <x:c r="H49" s="36"/>
       <x:c r="I49" s="36"/>
       <x:c r="J49" s="36"/>
       <x:c r="K49" s="10"/>
@@ -1519,7 +1616,7 @@
       <x:c r="E50" s="10"/>
       <x:c r="F50" s="10"/>
       <x:c r="G50" s="40"/>
-      <x:c r="H50" s="10"/>
+      <x:c r="H50" s="36"/>
       <x:c r="I50" s="36"/>
       <x:c r="J50" s="36"/>
       <x:c r="K50" s="10"/>
@@ -1534,7 +1631,7 @@
       <x:c r="E51" s="10"/>
       <x:c r="F51" s="10"/>
       <x:c r="G51" s="40"/>
-      <x:c r="H51" s="10"/>
+      <x:c r="H51" s="36"/>
       <x:c r="I51" s="36"/>
       <x:c r="J51" s="36"/>
       <x:c r="K51" s="10"/>
@@ -1549,7 +1646,7 @@
       <x:c r="E52" s="10"/>
       <x:c r="F52" s="10"/>
       <x:c r="G52" s="40"/>
-      <x:c r="H52" s="10"/>
+      <x:c r="H52" s="36"/>
       <x:c r="I52" s="36"/>
       <x:c r="J52" s="36"/>
       <x:c r="K52" s="10"/>
@@ -1564,7 +1661,7 @@
       <x:c r="E53" s="10"/>
       <x:c r="F53" s="10"/>
       <x:c r="G53" s="40"/>
-      <x:c r="H53" s="10"/>
+      <x:c r="H53" s="36"/>
       <x:c r="I53" s="36"/>
       <x:c r="J53" s="36"/>
       <x:c r="K53" s="10"/>
@@ -1579,7 +1676,7 @@
       <x:c r="E54" s="10"/>
       <x:c r="F54" s="10"/>
       <x:c r="G54" s="40"/>
-      <x:c r="H54" s="10"/>
+      <x:c r="H54" s="36"/>
       <x:c r="I54" s="36"/>
       <x:c r="J54" s="36"/>
       <x:c r="K54" s="10"/>
@@ -1594,7 +1691,7 @@
       <x:c r="E55" s="10"/>
       <x:c r="F55" s="10"/>
       <x:c r="G55" s="40"/>
-      <x:c r="H55" s="10"/>
+      <x:c r="H55" s="36"/>
       <x:c r="I55" s="36"/>
       <x:c r="J55" s="36"/>
       <x:c r="K55" s="10"/>
@@ -1609,7 +1706,7 @@
       <x:c r="E56" s="10"/>
       <x:c r="F56" s="10"/>
       <x:c r="G56" s="40"/>
-      <x:c r="H56" s="10"/>
+      <x:c r="H56" s="36"/>
       <x:c r="I56" s="36"/>
       <x:c r="J56" s="36"/>
       <x:c r="K56" s="10"/>
@@ -1624,7 +1721,7 @@
       <x:c r="E57" s="10"/>
       <x:c r="F57" s="10"/>
       <x:c r="G57" s="40"/>
-      <x:c r="H57" s="10"/>
+      <x:c r="H57" s="36"/>
       <x:c r="I57" s="36"/>
       <x:c r="J57" s="36"/>
       <x:c r="K57" s="10"/>
@@ -1639,7 +1736,7 @@
       <x:c r="E58" s="10"/>
       <x:c r="F58" s="10"/>
       <x:c r="G58" s="40"/>
-      <x:c r="H58" s="10"/>
+      <x:c r="H58" s="36"/>
       <x:c r="I58" s="36"/>
       <x:c r="J58" s="36"/>
       <x:c r="K58" s="10"/>
@@ -1654,7 +1751,7 @@
       <x:c r="E59" s="10"/>
       <x:c r="F59" s="10"/>
       <x:c r="G59" s="40"/>
-      <x:c r="H59" s="10"/>
+      <x:c r="H59" s="36"/>
       <x:c r="I59" s="36"/>
       <x:c r="J59" s="36"/>
       <x:c r="K59" s="10"/>
@@ -1669,7 +1766,7 @@
       <x:c r="E60" s="10"/>
       <x:c r="F60" s="10"/>
       <x:c r="G60" s="40"/>
-      <x:c r="H60" s="10"/>
+      <x:c r="H60" s="36"/>
       <x:c r="I60" s="36"/>
       <x:c r="J60" s="36"/>
       <x:c r="K60" s="10"/>
@@ -1684,7 +1781,7 @@
       <x:c r="E61" s="10"/>
       <x:c r="F61" s="10"/>
       <x:c r="G61" s="40"/>
-      <x:c r="H61" s="10"/>
+      <x:c r="H61" s="36"/>
       <x:c r="I61" s="36"/>
       <x:c r="J61" s="36"/>
       <x:c r="K61" s="10"/>
@@ -1699,7 +1796,7 @@
       <x:c r="E62" s="10"/>
       <x:c r="F62" s="10"/>
       <x:c r="G62" s="40"/>
-      <x:c r="H62" s="10"/>
+      <x:c r="H62" s="36"/>
       <x:c r="I62" s="36"/>
       <x:c r="J62" s="36"/>
       <x:c r="K62" s="10"/>
@@ -1714,7 +1811,7 @@
       <x:c r="E63" s="10"/>
       <x:c r="F63" s="10"/>
       <x:c r="G63" s="40"/>
-      <x:c r="H63" s="10"/>
+      <x:c r="H63" s="36"/>
       <x:c r="I63" s="36"/>
       <x:c r="J63" s="36"/>
       <x:c r="K63" s="10"/>
@@ -1729,7 +1826,7 @@
       <x:c r="E64" s="10"/>
       <x:c r="F64" s="10"/>
       <x:c r="G64" s="40"/>
-      <x:c r="H64" s="10"/>
+      <x:c r="H64" s="36"/>
       <x:c r="I64" s="36"/>
       <x:c r="J64" s="36"/>
       <x:c r="K64" s="10"/>
@@ -1744,7 +1841,7 @@
       <x:c r="E65" s="10"/>
       <x:c r="F65" s="10"/>
       <x:c r="G65" s="40"/>
-      <x:c r="H65" s="10"/>
+      <x:c r="H65" s="36"/>
       <x:c r="I65" s="36"/>
       <x:c r="J65" s="36"/>
       <x:c r="K65" s="10"/>
@@ -1759,7 +1856,7 @@
       <x:c r="E66" s="10"/>
       <x:c r="F66" s="10"/>
       <x:c r="G66" s="40"/>
-      <x:c r="H66" s="10"/>
+      <x:c r="H66" s="36"/>
       <x:c r="I66" s="36"/>
       <x:c r="J66" s="36"/>
       <x:c r="K66" s="10"/>
@@ -1774,7 +1871,7 @@
       <x:c r="E67" s="10"/>
       <x:c r="F67" s="10"/>
       <x:c r="G67" s="40"/>
-      <x:c r="H67" s="10"/>
+      <x:c r="H67" s="36"/>
       <x:c r="I67" s="36"/>
       <x:c r="J67" s="36"/>
       <x:c r="K67" s="10"/>
@@ -1789,7 +1886,7 @@
       <x:c r="E68" s="10"/>
       <x:c r="F68" s="10"/>
       <x:c r="G68" s="40"/>
-      <x:c r="H68" s="10"/>
+      <x:c r="H68" s="36"/>
       <x:c r="I68" s="36"/>
       <x:c r="J68" s="36"/>
       <x:c r="K68" s="10"/>
@@ -1804,7 +1901,7 @@
       <x:c r="E69" s="10"/>
       <x:c r="F69" s="10"/>
       <x:c r="G69" s="40"/>
-      <x:c r="H69" s="10"/>
+      <x:c r="H69" s="36"/>
       <x:c r="I69" s="36"/>
       <x:c r="J69" s="36"/>
       <x:c r="K69" s="10"/>
@@ -1819,7 +1916,7 @@
       <x:c r="E70" s="10"/>
       <x:c r="F70" s="10"/>
       <x:c r="G70" s="40"/>
-      <x:c r="H70" s="10"/>
+      <x:c r="H70" s="36"/>
       <x:c r="I70" s="36"/>
       <x:c r="J70" s="36"/>
       <x:c r="K70" s="10"/>
@@ -1834,7 +1931,7 @@
       <x:c r="E71" s="10"/>
       <x:c r="F71" s="10"/>
       <x:c r="G71" s="40"/>
-      <x:c r="H71" s="10"/>
+      <x:c r="H71" s="36"/>
       <x:c r="I71" s="36"/>
       <x:c r="J71" s="36"/>
       <x:c r="K71" s="10"/>
@@ -1849,7 +1946,7 @@
       <x:c r="E72" s="10"/>
       <x:c r="F72" s="10"/>
       <x:c r="G72" s="40"/>
-      <x:c r="H72" s="10"/>
+      <x:c r="H72" s="36"/>
       <x:c r="I72" s="36"/>
       <x:c r="J72" s="36"/>
       <x:c r="K72" s="10"/>
@@ -1864,7 +1961,7 @@
       <x:c r="E73" s="10"/>
       <x:c r="F73" s="10"/>
       <x:c r="G73" s="40"/>
-      <x:c r="H73" s="10"/>
+      <x:c r="H73" s="36"/>
       <x:c r="I73" s="36"/>
       <x:c r="J73" s="36"/>
       <x:c r="K73" s="10"/>
@@ -1879,7 +1976,7 @@
       <x:c r="E74" s="10"/>
       <x:c r="F74" s="10"/>
       <x:c r="G74" s="40"/>
-      <x:c r="H74" s="10"/>
+      <x:c r="H74" s="36"/>
       <x:c r="I74" s="36"/>
       <x:c r="J74" s="36"/>
       <x:c r="K74" s="10"/>
@@ -1894,7 +1991,7 @@
       <x:c r="E75" s="10"/>
       <x:c r="F75" s="10"/>
       <x:c r="G75" s="40"/>
-      <x:c r="H75" s="10"/>
+      <x:c r="H75" s="36"/>
       <x:c r="I75" s="36"/>
       <x:c r="J75" s="36"/>
       <x:c r="K75" s="10"/>
@@ -1909,7 +2006,7 @@
       <x:c r="E76" s="10"/>
       <x:c r="F76" s="10"/>
       <x:c r="G76" s="40"/>
-      <x:c r="H76" s="10"/>
+      <x:c r="H76" s="36"/>
       <x:c r="I76" s="36"/>
       <x:c r="J76" s="36"/>
       <x:c r="K76" s="10"/>
@@ -1924,7 +2021,7 @@
       <x:c r="E77" s="10"/>
       <x:c r="F77" s="10"/>
       <x:c r="G77" s="40"/>
-      <x:c r="H77" s="10"/>
+      <x:c r="H77" s="36"/>
       <x:c r="I77" s="36"/>
       <x:c r="J77" s="36"/>
       <x:c r="K77" s="10"/>
@@ -1939,7 +2036,7 @@
       <x:c r="E78" s="10"/>
       <x:c r="F78" s="10"/>
       <x:c r="G78" s="40"/>
-      <x:c r="H78" s="10"/>
+      <x:c r="H78" s="36"/>
       <x:c r="I78" s="36"/>
       <x:c r="J78" s="36"/>
       <x:c r="K78" s="10"/>
@@ -1954,7 +2051,7 @@
       <x:c r="E79" s="10"/>
       <x:c r="F79" s="10"/>
       <x:c r="G79" s="40"/>
-      <x:c r="H79" s="10"/>
+      <x:c r="H79" s="36"/>
       <x:c r="I79" s="36"/>
       <x:c r="J79" s="36"/>
       <x:c r="K79" s="10"/>
@@ -1969,7 +2066,7 @@
       <x:c r="E80" s="10"/>
       <x:c r="F80" s="10"/>
       <x:c r="G80" s="40"/>
-      <x:c r="H80" s="10"/>
+      <x:c r="H80" s="36"/>
       <x:c r="I80" s="36"/>
       <x:c r="J80" s="36"/>
       <x:c r="K80" s="10"/>
@@ -1984,7 +2081,7 @@
       <x:c r="E81" s="10"/>
       <x:c r="F81" s="10"/>
       <x:c r="G81" s="40"/>
-      <x:c r="H81" s="10"/>
+      <x:c r="H81" s="36"/>
       <x:c r="I81" s="36"/>
       <x:c r="J81" s="36"/>
       <x:c r="K81" s="10"/>
@@ -1999,7 +2096,7 @@
       <x:c r="E82" s="10"/>
       <x:c r="F82" s="10"/>
       <x:c r="G82" s="40"/>
-      <x:c r="H82" s="10"/>
+      <x:c r="H82" s="36"/>
       <x:c r="I82" s="36"/>
       <x:c r="J82" s="36"/>
       <x:c r="K82" s="10"/>
@@ -2014,7 +2111,7 @@
       <x:c r="E83" s="10"/>
       <x:c r="F83" s="10"/>
       <x:c r="G83" s="40"/>
-      <x:c r="H83" s="10"/>
+      <x:c r="H83" s="36"/>
       <x:c r="I83" s="36"/>
       <x:c r="J83" s="36"/>
       <x:c r="K83" s="10"/>
@@ -2029,7 +2126,7 @@
       <x:c r="E84" s="10"/>
       <x:c r="F84" s="10"/>
       <x:c r="G84" s="40"/>
-      <x:c r="H84" s="10"/>
+      <x:c r="H84" s="36"/>
       <x:c r="I84" s="36"/>
       <x:c r="J84" s="36"/>
       <x:c r="K84" s="10"/>
@@ -2044,7 +2141,7 @@
       <x:c r="E85" s="10"/>
       <x:c r="F85" s="10"/>
       <x:c r="G85" s="40"/>
-      <x:c r="H85" s="10"/>
+      <x:c r="H85" s="36"/>
       <x:c r="I85" s="36"/>
       <x:c r="J85" s="36"/>
       <x:c r="K85" s="10"/>
@@ -2059,7 +2156,7 @@
       <x:c r="E86" s="10"/>
       <x:c r="F86" s="10"/>
       <x:c r="G86" s="40"/>
-      <x:c r="H86" s="10"/>
+      <x:c r="H86" s="36"/>
       <x:c r="I86" s="36"/>
       <x:c r="J86" s="36"/>
       <x:c r="K86" s="10"/>
@@ -2074,7 +2171,7 @@
       <x:c r="E87" s="10"/>
       <x:c r="F87" s="10"/>
       <x:c r="G87" s="40"/>
-      <x:c r="H87" s="10"/>
+      <x:c r="H87" s="36"/>
       <x:c r="I87" s="36"/>
       <x:c r="J87" s="36"/>
       <x:c r="K87" s="10"/>
@@ -2089,7 +2186,7 @@
       <x:c r="E88" s="10"/>
       <x:c r="F88" s="10"/>
       <x:c r="G88" s="40"/>
-      <x:c r="H88" s="10"/>
+      <x:c r="H88" s="36"/>
       <x:c r="I88" s="36"/>
       <x:c r="J88" s="36"/>
       <x:c r="K88" s="10"/>
@@ -2104,7 +2201,7 @@
       <x:c r="E89" s="10"/>
       <x:c r="F89" s="10"/>
       <x:c r="G89" s="40"/>
-      <x:c r="H89" s="10"/>
+      <x:c r="H89" s="36"/>
       <x:c r="I89" s="36"/>
       <x:c r="J89" s="36"/>
       <x:c r="K89" s="10"/>
@@ -2119,7 +2216,7 @@
       <x:c r="E90" s="10"/>
       <x:c r="F90" s="10"/>
       <x:c r="G90" s="40"/>
-      <x:c r="H90" s="10"/>
+      <x:c r="H90" s="36"/>
       <x:c r="I90" s="36"/>
       <x:c r="J90" s="36"/>
       <x:c r="K90" s="10"/>
@@ -2134,7 +2231,7 @@
       <x:c r="E91" s="10"/>
       <x:c r="F91" s="10"/>
       <x:c r="G91" s="40"/>
-      <x:c r="H91" s="10"/>
+      <x:c r="H91" s="36"/>
       <x:c r="I91" s="36"/>
       <x:c r="J91" s="36"/>
       <x:c r="K91" s="10"/>
@@ -2149,7 +2246,7 @@
       <x:c r="E92" s="10"/>
       <x:c r="F92" s="10"/>
       <x:c r="G92" s="40"/>
-      <x:c r="H92" s="10"/>
+      <x:c r="H92" s="36"/>
       <x:c r="I92" s="36"/>
       <x:c r="J92" s="36"/>
       <x:c r="K92" s="10"/>
@@ -2164,7 +2261,7 @@
       <x:c r="E93" s="10"/>
       <x:c r="F93" s="10"/>
       <x:c r="G93" s="40"/>
-      <x:c r="H93" s="10"/>
+      <x:c r="H93" s="36"/>
       <x:c r="I93" s="36"/>
       <x:c r="J93" s="36"/>
       <x:c r="K93" s="10"/>
@@ -2179,7 +2276,7 @@
       <x:c r="E94" s="10"/>
       <x:c r="F94" s="10"/>
       <x:c r="G94" s="40"/>
-      <x:c r="H94" s="10"/>
+      <x:c r="H94" s="36"/>
       <x:c r="I94" s="36"/>
       <x:c r="J94" s="36"/>
       <x:c r="K94" s="10"/>
@@ -2194,7 +2291,7 @@
       <x:c r="E95" s="10"/>
       <x:c r="F95" s="10"/>
       <x:c r="G95" s="40"/>
-      <x:c r="H95" s="10"/>
+      <x:c r="H95" s="36"/>
       <x:c r="I95" s="36"/>
       <x:c r="J95" s="36"/>
       <x:c r="K95" s="10"/>
@@ -2209,7 +2306,7 @@
       <x:c r="E96" s="10"/>
       <x:c r="F96" s="10"/>
       <x:c r="G96" s="40"/>
-      <x:c r="H96" s="10"/>
+      <x:c r="H96" s="36"/>
       <x:c r="I96" s="36"/>
       <x:c r="J96" s="36"/>
       <x:c r="K96" s="10"/>
@@ -2224,7 +2321,7 @@
       <x:c r="E97" s="10"/>
       <x:c r="F97" s="10"/>
       <x:c r="G97" s="40"/>
-      <x:c r="H97" s="10"/>
+      <x:c r="H97" s="36"/>
       <x:c r="I97" s="36"/>
       <x:c r="J97" s="36"/>
       <x:c r="K97" s="10"/>
@@ -2239,7 +2336,7 @@
       <x:c r="E98" s="10"/>
       <x:c r="F98" s="10"/>
       <x:c r="G98" s="40"/>
-      <x:c r="H98" s="10"/>
+      <x:c r="H98" s="36"/>
       <x:c r="I98" s="36"/>
       <x:c r="J98" s="36"/>
       <x:c r="K98" s="10"/>
@@ -2254,7 +2351,7 @@
       <x:c r="E99" s="10"/>
       <x:c r="F99" s="10"/>
       <x:c r="G99" s="40"/>
-      <x:c r="H99" s="10"/>
+      <x:c r="H99" s="36"/>
       <x:c r="I99" s="36"/>
       <x:c r="J99" s="36"/>
       <x:c r="K99" s="10"/>
@@ -2269,7 +2366,7 @@
       <x:c r="E100" s="10"/>
       <x:c r="F100" s="10"/>
       <x:c r="G100" s="40"/>
-      <x:c r="H100" s="10"/>
+      <x:c r="H100" s="36"/>
       <x:c r="I100" s="36"/>
       <x:c r="J100" s="36"/>
       <x:c r="K100" s="10"/>
@@ -2284,7 +2381,7 @@
       <x:c r="E101" s="10"/>
       <x:c r="F101" s="10"/>
       <x:c r="G101" s="40"/>
-      <x:c r="H101" s="10"/>
+      <x:c r="H101" s="36"/>
       <x:c r="I101" s="36"/>
       <x:c r="J101" s="36"/>
       <x:c r="K101" s="10"/>
@@ -2299,7 +2396,7 @@
       <x:c r="E102" s="10"/>
       <x:c r="F102" s="10"/>
       <x:c r="G102" s="40"/>
-      <x:c r="H102" s="10"/>
+      <x:c r="H102" s="36"/>
       <x:c r="I102" s="36"/>
       <x:c r="J102" s="36"/>
       <x:c r="K102" s="10"/>
@@ -2314,7 +2411,7 @@
       <x:c r="E103" s="10"/>
       <x:c r="F103" s="10"/>
       <x:c r="G103" s="40"/>
-      <x:c r="H103" s="10"/>
+      <x:c r="H103" s="36"/>
       <x:c r="I103" s="36"/>
       <x:c r="J103" s="36"/>
       <x:c r="K103" s="10"/>
@@ -2329,7 +2426,7 @@
       <x:c r="E104" s="10"/>
       <x:c r="F104" s="10"/>
       <x:c r="G104" s="40"/>
-      <x:c r="H104" s="10"/>
+      <x:c r="H104" s="36"/>
       <x:c r="I104" s="36"/>
       <x:c r="J104" s="36"/>
       <x:c r="K104" s="10"/>
@@ -2344,7 +2441,7 @@
       <x:c r="E105" s="10"/>
       <x:c r="F105" s="10"/>
       <x:c r="G105" s="40"/>
-      <x:c r="H105" s="10"/>
+      <x:c r="H105" s="36"/>
       <x:c r="I105" s="36"/>
       <x:c r="J105" s="36"/>
       <x:c r="K105" s="10"/>
@@ -2359,7 +2456,7 @@
       <x:c r="E106" s="10"/>
       <x:c r="F106" s="10"/>
       <x:c r="G106" s="40"/>
-      <x:c r="H106" s="10"/>
+      <x:c r="H106" s="36"/>
       <x:c r="I106" s="36"/>
       <x:c r="J106" s="36"/>
       <x:c r="K106" s="10"/>
@@ -2374,7 +2471,7 @@
       <x:c r="E107" s="10"/>
       <x:c r="F107" s="10"/>
       <x:c r="G107" s="40"/>
-      <x:c r="H107" s="10"/>
+      <x:c r="H107" s="36"/>
       <x:c r="I107" s="36"/>
       <x:c r="J107" s="36"/>
       <x:c r="K107" s="10"/>
@@ -2389,7 +2486,7 @@
       <x:c r="E108" s="10"/>
       <x:c r="F108" s="10"/>
       <x:c r="G108" s="40"/>
-      <x:c r="H108" s="10"/>
+      <x:c r="H108" s="36"/>
       <x:c r="I108" s="36"/>
       <x:c r="J108" s="36"/>
       <x:c r="K108" s="10"/>
@@ -2404,7 +2501,7 @@
       <x:c r="E109" s="10"/>
       <x:c r="F109" s="10"/>
       <x:c r="G109" s="40"/>
-      <x:c r="H109" s="10"/>
+      <x:c r="H109" s="36"/>
       <x:c r="I109" s="36"/>
       <x:c r="J109" s="36"/>
       <x:c r="K109" s="10"/>
@@ -2419,7 +2516,7 @@
       <x:c r="E110" s="10"/>
       <x:c r="F110" s="10"/>
       <x:c r="G110" s="40"/>
-      <x:c r="H110" s="10"/>
+      <x:c r="H110" s="36"/>
       <x:c r="I110" s="36"/>
       <x:c r="J110" s="36"/>
       <x:c r="K110" s="10"/>
@@ -2434,7 +2531,7 @@
       <x:c r="E111" s="10"/>
       <x:c r="F111" s="10"/>
       <x:c r="G111" s="40"/>
-      <x:c r="H111" s="10"/>
+      <x:c r="H111" s="36"/>
       <x:c r="I111" s="36"/>
       <x:c r="J111" s="36"/>
       <x:c r="K111" s="10"/>
@@ -2449,7 +2546,7 @@
       <x:c r="E112" s="10"/>
       <x:c r="F112" s="10"/>
       <x:c r="G112" s="40"/>
-      <x:c r="H112" s="10"/>
+      <x:c r="H112" s="36"/>
       <x:c r="I112" s="36"/>
       <x:c r="J112" s="36"/>
       <x:c r="K112" s="10"/>
@@ -2464,7 +2561,7 @@
       <x:c r="E113" s="10"/>
       <x:c r="F113" s="10"/>
       <x:c r="G113" s="40"/>
-      <x:c r="H113" s="10"/>
+      <x:c r="H113" s="36"/>
       <x:c r="I113" s="36"/>
       <x:c r="J113" s="36"/>
       <x:c r="K113" s="10"/>
@@ -2479,7 +2576,7 @@
       <x:c r="E114" s="10"/>
       <x:c r="F114" s="10"/>
       <x:c r="G114" s="40"/>
-      <x:c r="H114" s="10"/>
+      <x:c r="H114" s="36"/>
       <x:c r="I114" s="36"/>
       <x:c r="J114" s="36"/>
       <x:c r="K114" s="10"/>
@@ -2494,7 +2591,7 @@
       <x:c r="E115" s="10"/>
       <x:c r="F115" s="10"/>
       <x:c r="G115" s="40"/>
-      <x:c r="H115" s="10"/>
+      <x:c r="H115" s="36"/>
       <x:c r="I115" s="36"/>
       <x:c r="J115" s="36"/>
       <x:c r="K115" s="10"/>
@@ -2509,7 +2606,7 @@
       <x:c r="E116" s="10"/>
       <x:c r="F116" s="10"/>
       <x:c r="G116" s="40"/>
-      <x:c r="H116" s="10"/>
+      <x:c r="H116" s="36"/>
       <x:c r="I116" s="36"/>
       <x:c r="J116" s="36"/>
       <x:c r="K116" s="10"/>
@@ -2524,7 +2621,7 @@
       <x:c r="E117" s="10"/>
       <x:c r="F117" s="10"/>
       <x:c r="G117" s="40"/>
-      <x:c r="H117" s="10"/>
+      <x:c r="H117" s="36"/>
       <x:c r="I117" s="36"/>
       <x:c r="J117" s="36"/>
       <x:c r="K117" s="10"/>
@@ -2539,7 +2636,7 @@
       <x:c r="E118" s="10"/>
       <x:c r="F118" s="10"/>
       <x:c r="G118" s="40"/>
-      <x:c r="H118" s="10"/>
+      <x:c r="H118" s="36"/>
       <x:c r="I118" s="36"/>
       <x:c r="J118" s="36"/>
       <x:c r="K118" s="10"/>
@@ -2554,7 +2651,7 @@
       <x:c r="E119" s="10"/>
       <x:c r="F119" s="10"/>
       <x:c r="G119" s="40"/>
-      <x:c r="H119" s="10"/>
+      <x:c r="H119" s="36"/>
       <x:c r="I119" s="36"/>
       <x:c r="J119" s="36"/>
       <x:c r="K119" s="10"/>
@@ -2569,7 +2666,7 @@
       <x:c r="E120" s="10"/>
       <x:c r="F120" s="10"/>
       <x:c r="G120" s="40"/>
-      <x:c r="H120" s="10"/>
+      <x:c r="H120" s="36"/>
       <x:c r="I120" s="36"/>
       <x:c r="J120" s="36"/>
       <x:c r="K120" s="10"/>
@@ -2584,7 +2681,7 @@
       <x:c r="E121" s="10"/>
       <x:c r="F121" s="10"/>
       <x:c r="G121" s="40"/>
-      <x:c r="H121" s="10"/>
+      <x:c r="H121" s="36"/>
       <x:c r="I121" s="36"/>
       <x:c r="J121" s="36"/>
       <x:c r="K121" s="10"/>
@@ -2599,7 +2696,7 @@
       <x:c r="E122" s="10"/>
       <x:c r="F122" s="10"/>
       <x:c r="G122" s="40"/>
-      <x:c r="H122" s="10"/>
+      <x:c r="H122" s="36"/>
       <x:c r="I122" s="36"/>
       <x:c r="J122" s="36"/>
       <x:c r="K122" s="10"/>
@@ -2614,7 +2711,7 @@
       <x:c r="E123" s="10"/>
       <x:c r="F123" s="10"/>
       <x:c r="G123" s="40"/>
-      <x:c r="H123" s="10"/>
+      <x:c r="H123" s="36"/>
       <x:c r="I123" s="36"/>
       <x:c r="J123" s="36"/>
       <x:c r="K123" s="10"/>
@@ -2629,7 +2726,7 @@
       <x:c r="E124" s="10"/>
       <x:c r="F124" s="10"/>
       <x:c r="G124" s="40"/>
-      <x:c r="H124" s="10"/>
+      <x:c r="H124" s="36"/>
       <x:c r="I124" s="36"/>
       <x:c r="J124" s="36"/>
       <x:c r="K124" s="10"/>
@@ -2644,7 +2741,7 @@
       <x:c r="E125" s="10"/>
       <x:c r="F125" s="10"/>
       <x:c r="G125" s="40"/>
-      <x:c r="H125" s="10"/>
+      <x:c r="H125" s="36"/>
       <x:c r="I125" s="36"/>
       <x:c r="J125" s="36"/>
       <x:c r="K125" s="10"/>
@@ -2659,7 +2756,7 @@
       <x:c r="E126" s="10"/>
       <x:c r="F126" s="10"/>
       <x:c r="G126" s="40"/>
-      <x:c r="H126" s="10"/>
+      <x:c r="H126" s="36"/>
       <x:c r="I126" s="36"/>
       <x:c r="J126" s="36"/>
       <x:c r="K126" s="10"/>
@@ -2674,7 +2771,7 @@
       <x:c r="E127" s="10"/>
       <x:c r="F127" s="10"/>
       <x:c r="G127" s="40"/>
-      <x:c r="H127" s="10"/>
+      <x:c r="H127" s="36"/>
       <x:c r="I127" s="36"/>
       <x:c r="J127" s="36"/>
       <x:c r="K127" s="10"/>
@@ -2689,7 +2786,7 @@
       <x:c r="E128" s="10"/>
       <x:c r="F128" s="10"/>
       <x:c r="G128" s="40"/>
-      <x:c r="H128" s="10"/>
+      <x:c r="H128" s="36"/>
       <x:c r="I128" s="36"/>
       <x:c r="J128" s="36"/>
       <x:c r="K128" s="10"/>
@@ -2704,7 +2801,7 @@
       <x:c r="E129" s="10"/>
       <x:c r="F129" s="10"/>
       <x:c r="G129" s="40"/>
-      <x:c r="H129" s="10"/>
+      <x:c r="H129" s="36"/>
       <x:c r="I129" s="36"/>
       <x:c r="J129" s="36"/>
       <x:c r="K129" s="10"/>
@@ -2719,7 +2816,7 @@
       <x:c r="E130" s="10"/>
       <x:c r="F130" s="10"/>
       <x:c r="G130" s="40"/>
-      <x:c r="H130" s="10"/>
+      <x:c r="H130" s="36"/>
       <x:c r="I130" s="36"/>
       <x:c r="J130" s="36"/>
       <x:c r="K130" s="10"/>
@@ -2734,7 +2831,7 @@
       <x:c r="E131" s="10"/>
       <x:c r="F131" s="10"/>
       <x:c r="G131" s="40"/>
-      <x:c r="H131" s="10"/>
+      <x:c r="H131" s="36"/>
       <x:c r="I131" s="36"/>
       <x:c r="J131" s="36"/>
       <x:c r="K131" s="10"/>
@@ -2749,7 +2846,7 @@
       <x:c r="E132" s="10"/>
       <x:c r="F132" s="10"/>
       <x:c r="G132" s="40"/>
-      <x:c r="H132" s="10"/>
+      <x:c r="H132" s="36"/>
       <x:c r="I132" s="36"/>
       <x:c r="J132" s="36"/>
       <x:c r="K132" s="10"/>
@@ -2764,7 +2861,7 @@
       <x:c r="E133" s="10"/>
       <x:c r="F133" s="10"/>
       <x:c r="G133" s="40"/>
-      <x:c r="H133" s="10"/>
+      <x:c r="H133" s="36"/>
       <x:c r="I133" s="36"/>
       <x:c r="J133" s="36"/>
       <x:c r="K133" s="10"/>
@@ -2779,7 +2876,7 @@
       <x:c r="E134" s="10"/>
       <x:c r="F134" s="10"/>
       <x:c r="G134" s="40"/>
-      <x:c r="H134" s="10"/>
+      <x:c r="H134" s="36"/>
       <x:c r="I134" s="36"/>
       <x:c r="J134" s="36"/>
       <x:c r="K134" s="10"/>
@@ -2794,7 +2891,7 @@
       <x:c r="E135" s="10"/>
       <x:c r="F135" s="10"/>
       <x:c r="G135" s="40"/>
-      <x:c r="H135" s="10"/>
+      <x:c r="H135" s="36"/>
       <x:c r="I135" s="36"/>
       <x:c r="J135" s="36"/>
       <x:c r="K135" s="10"/>
@@ -2809,7 +2906,7 @@
       <x:c r="E136" s="10"/>
       <x:c r="F136" s="10"/>
       <x:c r="G136" s="40"/>
-      <x:c r="H136" s="10"/>
+      <x:c r="H136" s="36"/>
       <x:c r="I136" s="36"/>
       <x:c r="J136" s="36"/>
       <x:c r="K136" s="10"/>
@@ -2824,7 +2921,7 @@
       <x:c r="E137" s="10"/>
       <x:c r="F137" s="10"/>
       <x:c r="G137" s="40"/>
-      <x:c r="H137" s="10"/>
+      <x:c r="H137" s="36"/>
       <x:c r="I137" s="36"/>
       <x:c r="J137" s="36"/>
       <x:c r="K137" s="10"/>
@@ -2839,7 +2936,7 @@
       <x:c r="E138" s="10"/>
       <x:c r="F138" s="10"/>
       <x:c r="G138" s="40"/>
-      <x:c r="H138" s="10"/>
+      <x:c r="H138" s="36"/>
       <x:c r="I138" s="36"/>
       <x:c r="J138" s="36"/>
       <x:c r="K138" s="10"/>
@@ -2854,7 +2951,7 @@
       <x:c r="E139" s="10"/>
       <x:c r="F139" s="10"/>
       <x:c r="G139" s="40"/>
-      <x:c r="H139" s="10"/>
+      <x:c r="H139" s="36"/>
       <x:c r="I139" s="36"/>
       <x:c r="J139" s="36"/>
       <x:c r="K139" s="10"/>
@@ -2869,7 +2966,7 @@
       <x:c r="E140" s="10"/>
       <x:c r="F140" s="10"/>
       <x:c r="G140" s="40"/>
-      <x:c r="H140" s="10"/>
+      <x:c r="H140" s="36"/>
       <x:c r="I140" s="36"/>
       <x:c r="J140" s="36"/>
       <x:c r="K140" s="10"/>
@@ -2884,7 +2981,7 @@
       <x:c r="E141" s="10"/>
       <x:c r="F141" s="10"/>
       <x:c r="G141" s="40"/>
-      <x:c r="H141" s="10"/>
+      <x:c r="H141" s="36"/>
       <x:c r="I141" s="36"/>
       <x:c r="J141" s="36"/>
       <x:c r="K141" s="10"/>
@@ -2899,7 +2996,7 @@
       <x:c r="E142" s="10"/>
       <x:c r="F142" s="10"/>
       <x:c r="G142" s="40"/>
-      <x:c r="H142" s="10"/>
+      <x:c r="H142" s="36"/>
       <x:c r="I142" s="36"/>
       <x:c r="J142" s="36"/>
       <x:c r="K142" s="10"/>
@@ -2914,7 +3011,7 @@
       <x:c r="E143" s="10"/>
       <x:c r="F143" s="10"/>
       <x:c r="G143" s="40"/>
-      <x:c r="H143" s="10"/>
+      <x:c r="H143" s="36"/>
       <x:c r="I143" s="36"/>
       <x:c r="J143" s="36"/>
       <x:c r="K143" s="10"/>
@@ -2929,7 +3026,7 @@
       <x:c r="E144" s="10"/>
       <x:c r="F144" s="10"/>
       <x:c r="G144" s="40"/>
-      <x:c r="H144" s="10"/>
+      <x:c r="H144" s="36"/>
       <x:c r="I144" s="36"/>
       <x:c r="J144" s="36"/>
       <x:c r="K144" s="10"/>
@@ -2944,7 +3041,7 @@
       <x:c r="E145" s="10"/>
       <x:c r="F145" s="10"/>
       <x:c r="G145" s="40"/>
-      <x:c r="H145" s="10"/>
+      <x:c r="H145" s="36"/>
       <x:c r="I145" s="36"/>
       <x:c r="J145" s="36"/>
       <x:c r="K145" s="10"/>
@@ -2959,7 +3056,7 @@
       <x:c r="E146" s="10"/>
       <x:c r="F146" s="10"/>
       <x:c r="G146" s="40"/>
-      <x:c r="H146" s="10"/>
+      <x:c r="H146" s="36"/>
       <x:c r="I146" s="36"/>
       <x:c r="J146" s="36"/>
       <x:c r="K146" s="10"/>
@@ -2974,7 +3071,7 @@
       <x:c r="E147" s="10"/>
       <x:c r="F147" s="10"/>
       <x:c r="G147" s="40"/>
-      <x:c r="H147" s="10"/>
+      <x:c r="H147" s="36"/>
       <x:c r="I147" s="36"/>
       <x:c r="J147" s="36"/>
       <x:c r="K147" s="10"/>
@@ -2989,7 +3086,7 @@
       <x:c r="E148" s="10"/>
       <x:c r="F148" s="10"/>
       <x:c r="G148" s="40"/>
-      <x:c r="H148" s="10"/>
+      <x:c r="H148" s="36"/>
       <x:c r="I148" s="36"/>
       <x:c r="J148" s="36"/>
       <x:c r="K148" s="10"/>
@@ -3004,7 +3101,7 @@
       <x:c r="E149" s="10"/>
       <x:c r="F149" s="10"/>
       <x:c r="G149" s="40"/>
-      <x:c r="H149" s="10"/>
+      <x:c r="H149" s="36"/>
       <x:c r="I149" s="36"/>
       <x:c r="J149" s="36"/>
       <x:c r="K149" s="10"/>
@@ -3019,7 +3116,7 @@
       <x:c r="E150" s="10"/>
       <x:c r="F150" s="10"/>
       <x:c r="G150" s="40"/>
-      <x:c r="H150" s="10"/>
+      <x:c r="H150" s="36"/>
       <x:c r="I150" s="36"/>
       <x:c r="J150" s="36"/>
       <x:c r="K150" s="10"/>
@@ -3034,7 +3131,7 @@
       <x:c r="E151" s="10"/>
       <x:c r="F151" s="10"/>
       <x:c r="G151" s="40"/>
-      <x:c r="H151" s="10"/>
+      <x:c r="H151" s="36"/>
       <x:c r="I151" s="36"/>
       <x:c r="J151" s="36"/>
       <x:c r="K151" s="10"/>
@@ -3049,7 +3146,7 @@
       <x:c r="E152" s="10"/>
       <x:c r="F152" s="10"/>
       <x:c r="G152" s="40"/>
-      <x:c r="H152" s="10"/>
+      <x:c r="H152" s="36"/>
       <x:c r="I152" s="36"/>
       <x:c r="J152" s="36"/>
       <x:c r="K152" s="10"/>
@@ -3064,7 +3161,7 @@
       <x:c r="E153" s="10"/>
       <x:c r="F153" s="10"/>
       <x:c r="G153" s="40"/>
-      <x:c r="H153" s="10"/>
+      <x:c r="H153" s="36"/>
       <x:c r="I153" s="36"/>
       <x:c r="J153" s="36"/>
       <x:c r="K153" s="10"/>
@@ -3079,7 +3176,7 @@
       <x:c r="E154" s="10"/>
       <x:c r="F154" s="10"/>
       <x:c r="G154" s="40"/>
-      <x:c r="H154" s="10"/>
+      <x:c r="H154" s="36"/>
       <x:c r="I154" s="36"/>
       <x:c r="J154" s="36"/>
       <x:c r="K154" s="10"/>
@@ -3094,7 +3191,7 @@
       <x:c r="E155" s="10"/>
       <x:c r="F155" s="10"/>
       <x:c r="G155" s="40"/>
-      <x:c r="H155" s="10"/>
+      <x:c r="H155" s="36"/>
       <x:c r="I155" s="36"/>
       <x:c r="J155" s="36"/>
       <x:c r="K155" s="10"/>
@@ -3109,7 +3206,7 @@
       <x:c r="E156" s="10"/>
       <x:c r="F156" s="10"/>
       <x:c r="G156" s="40"/>
-      <x:c r="H156" s="10"/>
+      <x:c r="H156" s="36"/>
       <x:c r="I156" s="36"/>
       <x:c r="J156" s="36"/>
       <x:c r="K156" s="10"/>
@@ -3124,7 +3221,7 @@
       <x:c r="E157" s="10"/>
       <x:c r="F157" s="10"/>
       <x:c r="G157" s="40"/>
-      <x:c r="H157" s="10"/>
+      <x:c r="H157" s="36"/>
       <x:c r="I157" s="36"/>
       <x:c r="J157" s="36"/>
       <x:c r="K157" s="10"/>
@@ -3139,7 +3236,7 @@
       <x:c r="E158" s="10"/>
       <x:c r="F158" s="10"/>
       <x:c r="G158" s="40"/>
-      <x:c r="H158" s="10"/>
+      <x:c r="H158" s="36"/>
       <x:c r="I158" s="36"/>
       <x:c r="J158" s="36"/>
       <x:c r="K158" s="10"/>
@@ -3154,7 +3251,7 @@
       <x:c r="E159" s="10"/>
       <x:c r="F159" s="10"/>
       <x:c r="G159" s="40"/>
-      <x:c r="H159" s="10"/>
+      <x:c r="H159" s="36"/>
       <x:c r="I159" s="36"/>
       <x:c r="J159" s="36"/>
       <x:c r="K159" s="10"/>
@@ -3169,7 +3266,7 @@
       <x:c r="E160" s="10"/>
       <x:c r="F160" s="10"/>
       <x:c r="G160" s="40"/>
-      <x:c r="H160" s="10"/>
+      <x:c r="H160" s="36"/>
       <x:c r="I160" s="36"/>
       <x:c r="J160" s="36"/>
       <x:c r="K160" s="10"/>
@@ -3184,7 +3281,7 @@
       <x:c r="E161" s="10"/>
       <x:c r="F161" s="10"/>
       <x:c r="G161" s="40"/>
-      <x:c r="H161" s="10"/>
+      <x:c r="H161" s="36"/>
       <x:c r="I161" s="36"/>
       <x:c r="J161" s="36"/>
       <x:c r="K161" s="10"/>
@@ -3199,7 +3296,7 @@
       <x:c r="E162" s="10"/>
       <x:c r="F162" s="10"/>
       <x:c r="G162" s="40"/>
-      <x:c r="H162" s="10"/>
+      <x:c r="H162" s="36"/>
       <x:c r="I162" s="36"/>
       <x:c r="J162" s="36"/>
       <x:c r="K162" s="10"/>
@@ -3214,7 +3311,7 @@
       <x:c r="E163" s="10"/>
       <x:c r="F163" s="10"/>
       <x:c r="G163" s="40"/>
-      <x:c r="H163" s="10"/>
+      <x:c r="H163" s="36"/>
       <x:c r="I163" s="36"/>
       <x:c r="J163" s="36"/>
       <x:c r="K163" s="10"/>
@@ -3229,7 +3326,7 @@
       <x:c r="E164" s="10"/>
       <x:c r="F164" s="10"/>
       <x:c r="G164" s="40"/>
-      <x:c r="H164" s="10"/>
+      <x:c r="H164" s="36"/>
       <x:c r="I164" s="36"/>
       <x:c r="J164" s="36"/>
       <x:c r="K164" s="10"/>
@@ -3244,7 +3341,7 @@
       <x:c r="E165" s="10"/>
       <x:c r="F165" s="10"/>
       <x:c r="G165" s="40"/>
-      <x:c r="H165" s="10"/>
+      <x:c r="H165" s="36"/>
       <x:c r="I165" s="36"/>
       <x:c r="J165" s="36"/>
       <x:c r="K165" s="10"/>
@@ -3259,7 +3356,7 @@
       <x:c r="E166" s="10"/>
       <x:c r="F166" s="10"/>
       <x:c r="G166" s="40"/>
-      <x:c r="H166" s="10"/>
+      <x:c r="H166" s="36"/>
       <x:c r="I166" s="36"/>
       <x:c r="J166" s="36"/>
       <x:c r="K166" s="10"/>
@@ -3274,7 +3371,7 @@
       <x:c r="E167" s="10"/>
       <x:c r="F167" s="10"/>
       <x:c r="G167" s="40"/>
-      <x:c r="H167" s="10"/>
+      <x:c r="H167" s="36"/>
       <x:c r="I167" s="36"/>
       <x:c r="J167" s="36"/>
       <x:c r="K167" s="10"/>
@@ -3289,7 +3386,7 @@
       <x:c r="E168" s="10"/>
       <x:c r="F168" s="10"/>
       <x:c r="G168" s="40"/>
-      <x:c r="H168" s="10"/>
+      <x:c r="H168" s="36"/>
       <x:c r="I168" s="36"/>
       <x:c r="J168" s="36"/>
       <x:c r="K168" s="10"/>
@@ -3304,7 +3401,7 @@
       <x:c r="E169" s="10"/>
       <x:c r="F169" s="10"/>
       <x:c r="G169" s="40"/>
-      <x:c r="H169" s="10"/>
+      <x:c r="H169" s="36"/>
       <x:c r="I169" s="36"/>
       <x:c r="J169" s="36"/>
       <x:c r="K169" s="10"/>
@@ -3319,7 +3416,7 @@
       <x:c r="E170" s="10"/>
       <x:c r="F170" s="10"/>
       <x:c r="G170" s="40"/>
-      <x:c r="H170" s="10"/>
+      <x:c r="H170" s="36"/>
       <x:c r="I170" s="36"/>
       <x:c r="J170" s="36"/>
       <x:c r="K170" s="10"/>
@@ -3334,7 +3431,7 @@
       <x:c r="E171" s="10"/>
       <x:c r="F171" s="10"/>
       <x:c r="G171" s="40"/>
-      <x:c r="H171" s="10"/>
+      <x:c r="H171" s="36"/>
       <x:c r="I171" s="36"/>
       <x:c r="J171" s="36"/>
       <x:c r="K171" s="10"/>
@@ -3349,7 +3446,7 @@
       <x:c r="E172" s="10"/>
       <x:c r="F172" s="10"/>
       <x:c r="G172" s="40"/>
-      <x:c r="H172" s="10"/>
+      <x:c r="H172" s="36"/>
       <x:c r="I172" s="36"/>
       <x:c r="J172" s="36"/>
       <x:c r="K172" s="10"/>
@@ -3364,7 +3461,7 @@
       <x:c r="E173" s="10"/>
       <x:c r="F173" s="10"/>
       <x:c r="G173" s="40"/>
-      <x:c r="H173" s="10"/>
+      <x:c r="H173" s="36"/>
       <x:c r="I173" s="36"/>
       <x:c r="J173" s="36"/>
       <x:c r="K173" s="10"/>
@@ -3379,7 +3476,7 @@
       <x:c r="E174" s="10"/>
       <x:c r="F174" s="10"/>
       <x:c r="G174" s="40"/>
-      <x:c r="H174" s="10"/>
+      <x:c r="H174" s="36"/>
       <x:c r="I174" s="36"/>
       <x:c r="J174" s="36"/>
       <x:c r="K174" s="10"/>
@@ -3394,7 +3491,7 @@
       <x:c r="E175" s="10"/>
       <x:c r="F175" s="10"/>
       <x:c r="G175" s="40"/>
-      <x:c r="H175" s="10"/>
+      <x:c r="H175" s="36"/>
       <x:c r="I175" s="36"/>
       <x:c r="J175" s="36"/>
       <x:c r="K175" s="10"/>
@@ -3409,7 +3506,7 @@
       <x:c r="E176" s="10"/>
       <x:c r="F176" s="10"/>
       <x:c r="G176" s="40"/>
-      <x:c r="H176" s="10"/>
+      <x:c r="H176" s="36"/>
       <x:c r="I176" s="36"/>
       <x:c r="J176" s="36"/>
       <x:c r="K176" s="10"/>
@@ -3424,7 +3521,7 @@
       <x:c r="E177" s="10"/>
       <x:c r="F177" s="10"/>
       <x:c r="G177" s="40"/>
-      <x:c r="H177" s="10"/>
+      <x:c r="H177" s="36"/>
       <x:c r="I177" s="36"/>
       <x:c r="J177" s="36"/>
       <x:c r="K177" s="10"/>
@@ -3439,7 +3536,7 @@
       <x:c r="E178" s="10"/>
       <x:c r="F178" s="10"/>
       <x:c r="G178" s="40"/>
-      <x:c r="H178" s="10"/>
+      <x:c r="H178" s="36"/>
       <x:c r="I178" s="36"/>
       <x:c r="J178" s="36"/>
       <x:c r="K178" s="10"/>
@@ -3454,7 +3551,7 @@
       <x:c r="E179" s="10"/>
       <x:c r="F179" s="10"/>
       <x:c r="G179" s="40"/>
-      <x:c r="H179" s="10"/>
+      <x:c r="H179" s="36"/>
       <x:c r="I179" s="36"/>
       <x:c r="J179" s="36"/>
       <x:c r="K179" s="10"/>
@@ -3469,7 +3566,7 @@
       <x:c r="E180" s="10"/>
       <x:c r="F180" s="10"/>
       <x:c r="G180" s="40"/>
-      <x:c r="H180" s="10"/>
+      <x:c r="H180" s="36"/>
       <x:c r="I180" s="36"/>
       <x:c r="J180" s="36"/>
       <x:c r="K180" s="10"/>
@@ -3484,7 +3581,7 @@
       <x:c r="E181" s="10"/>
       <x:c r="F181" s="10"/>
       <x:c r="G181" s="40"/>
-      <x:c r="H181" s="10"/>
+      <x:c r="H181" s="36"/>
       <x:c r="I181" s="36"/>
       <x:c r="J181" s="36"/>
       <x:c r="K181" s="10"/>
@@ -3499,7 +3596,7 @@
       <x:c r="E182" s="10"/>
       <x:c r="F182" s="10"/>
       <x:c r="G182" s="40"/>
-      <x:c r="H182" s="10"/>
+      <x:c r="H182" s="36"/>
       <x:c r="I182" s="36"/>
       <x:c r="J182" s="36"/>
       <x:c r="K182" s="10"/>
@@ -3514,7 +3611,7 @@
       <x:c r="E183" s="10"/>
       <x:c r="F183" s="10"/>
       <x:c r="G183" s="40"/>
-      <x:c r="H183" s="10"/>
+      <x:c r="H183" s="36"/>
       <x:c r="I183" s="36"/>
       <x:c r="J183" s="36"/>
       <x:c r="K183" s="10"/>
@@ -3529,7 +3626,7 @@
       <x:c r="E184" s="10"/>
       <x:c r="F184" s="10"/>
       <x:c r="G184" s="40"/>
-      <x:c r="H184" s="10"/>
+      <x:c r="H184" s="36"/>
       <x:c r="I184" s="36"/>
       <x:c r="J184" s="36"/>
       <x:c r="K184" s="10"/>
@@ -3544,7 +3641,7 @@
       <x:c r="E185" s="10"/>
       <x:c r="F185" s="10"/>
       <x:c r="G185" s="40"/>
-      <x:c r="H185" s="10"/>
+      <x:c r="H185" s="36"/>
       <x:c r="I185" s="36"/>
       <x:c r="J185" s="36"/>
       <x:c r="K185" s="10"/>
@@ -3559,7 +3656,7 @@
       <x:c r="E186" s="10"/>
       <x:c r="F186" s="10"/>
       <x:c r="G186" s="40"/>
-      <x:c r="H186" s="10"/>
+      <x:c r="H186" s="36"/>
       <x:c r="I186" s="36"/>
       <x:c r="J186" s="36"/>
       <x:c r="K186" s="10"/>
@@ -3574,7 +3671,7 @@
       <x:c r="E187" s="10"/>
       <x:c r="F187" s="10"/>
       <x:c r="G187" s="40"/>
-      <x:c r="H187" s="10"/>
+      <x:c r="H187" s="36"/>
       <x:c r="I187" s="36"/>
       <x:c r="J187" s="36"/>
       <x:c r="K187" s="10"/>
@@ -3589,7 +3686,7 @@
       <x:c r="E188" s="10"/>
       <x:c r="F188" s="10"/>
       <x:c r="G188" s="40"/>
-      <x:c r="H188" s="10"/>
+      <x:c r="H188" s="36"/>
       <x:c r="I188" s="36"/>
       <x:c r="J188" s="36"/>
       <x:c r="K188" s="10"/>
@@ -3604,7 +3701,7 @@
       <x:c r="E189" s="10"/>
       <x:c r="F189" s="10"/>
       <x:c r="G189" s="40"/>
-      <x:c r="H189" s="10"/>
+      <x:c r="H189" s="36"/>
       <x:c r="I189" s="36"/>
       <x:c r="J189" s="36"/>
       <x:c r="K189" s="10"/>
@@ -3619,7 +3716,7 @@
       <x:c r="E190" s="10"/>
       <x:c r="F190" s="10"/>
       <x:c r="G190" s="40"/>
-      <x:c r="H190" s="10"/>
+      <x:c r="H190" s="36"/>
       <x:c r="I190" s="36"/>
       <x:c r="J190" s="36"/>
       <x:c r="K190" s="10"/>
@@ -3634,7 +3731,7 @@
       <x:c r="E191" s="10"/>
       <x:c r="F191" s="10"/>
       <x:c r="G191" s="40"/>
-      <x:c r="H191" s="10"/>
+      <x:c r="H191" s="36"/>
       <x:c r="I191" s="36"/>
       <x:c r="J191" s="36"/>
       <x:c r="K191" s="10"/>
@@ -3649,7 +3746,7 @@
       <x:c r="E192" s="10"/>
       <x:c r="F192" s="10"/>
       <x:c r="G192" s="40"/>
-      <x:c r="H192" s="10"/>
+      <x:c r="H192" s="36"/>
       <x:c r="I192" s="36"/>
       <x:c r="J192" s="36"/>
       <x:c r="K192" s="10"/>
@@ -3664,7 +3761,7 @@
       <x:c r="E193" s="10"/>
       <x:c r="F193" s="10"/>
       <x:c r="G193" s="40"/>
-      <x:c r="H193" s="10"/>
+      <x:c r="H193" s="36"/>
       <x:c r="I193" s="36"/>
       <x:c r="J193" s="36"/>
       <x:c r="K193" s="10"/>
@@ -3679,7 +3776,7 @@
       <x:c r="E194" s="10"/>
       <x:c r="F194" s="10"/>
       <x:c r="G194" s="40"/>
-      <x:c r="H194" s="10"/>
+      <x:c r="H194" s="36"/>
       <x:c r="I194" s="36"/>
       <x:c r="J194" s="36"/>
       <x:c r="K194" s="10"/>
@@ -3694,7 +3791,7 @@
       <x:c r="E195" s="10"/>
       <x:c r="F195" s="10"/>
       <x:c r="G195" s="40"/>
-      <x:c r="H195" s="10"/>
+      <x:c r="H195" s="36"/>
       <x:c r="I195" s="36"/>
       <x:c r="J195" s="36"/>
       <x:c r="K195" s="10"/>
@@ -3709,7 +3806,7 @@
       <x:c r="E196" s="10"/>
       <x:c r="F196" s="10"/>
       <x:c r="G196" s="40"/>
-      <x:c r="H196" s="10"/>
+      <x:c r="H196" s="36"/>
       <x:c r="I196" s="36"/>
       <x:c r="J196" s="36"/>
       <x:c r="K196" s="10"/>
@@ -3724,7 +3821,7 @@
       <x:c r="E197" s="10"/>
       <x:c r="F197" s="10"/>
       <x:c r="G197" s="40"/>
-      <x:c r="H197" s="10"/>
+      <x:c r="H197" s="36"/>
       <x:c r="I197" s="36"/>
       <x:c r="J197" s="36"/>
       <x:c r="K197" s="10"/>
@@ -3739,7 +3836,7 @@
       <x:c r="E198" s="10"/>
       <x:c r="F198" s="10"/>
       <x:c r="G198" s="40"/>
-      <x:c r="H198" s="10"/>
+      <x:c r="H198" s="36"/>
       <x:c r="I198" s="36"/>
       <x:c r="J198" s="36"/>
       <x:c r="K198" s="10"/>
@@ -3754,7 +3851,7 @@
       <x:c r="E199" s="10"/>
       <x:c r="F199" s="10"/>
       <x:c r="G199" s="40"/>
-      <x:c r="H199" s="10"/>
+      <x:c r="H199" s="36"/>
       <x:c r="I199" s="36"/>
       <x:c r="J199" s="36"/>
       <x:c r="K199" s="10"/>
@@ -3769,12 +3866,3212 @@
       <x:c r="E200" s="10"/>
       <x:c r="F200" s="10"/>
       <x:c r="G200" s="40"/>
-      <x:c r="H200" s="10"/>
+      <x:c r="H200" s="36"/>
       <x:c r="I200" s="36"/>
       <x:c r="J200" s="36"/>
       <x:c r="K200" s="10"/>
       <x:c r="L200" s="10"/>
       <x:c r="M200" s="10"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="G201" s="41"/>
+      <x:c r="H201" s="42"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="G202" s="41"/>
+      <x:c r="H202" s="42"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="G203" s="41"/>
+      <x:c r="H203" s="42"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="G204" s="41"/>
+      <x:c r="H204" s="42"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="G205" s="41"/>
+      <x:c r="H205" s="42"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="G206" s="41"/>
+      <x:c r="H206" s="42"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="G207" s="41"/>
+      <x:c r="H207" s="42"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="G208" s="41"/>
+      <x:c r="H208" s="42"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="G209" s="41"/>
+      <x:c r="H209" s="42"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="G210" s="41"/>
+      <x:c r="H210" s="42"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="G211" s="41"/>
+      <x:c r="H211" s="42"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="G212" s="41"/>
+      <x:c r="H212" s="42"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="G213" s="41"/>
+      <x:c r="H213" s="42"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="G214" s="41"/>
+      <x:c r="H214" s="42"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="G215" s="41"/>
+      <x:c r="H215" s="42"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="G216" s="41"/>
+      <x:c r="H216" s="42"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="G217" s="41"/>
+      <x:c r="H217" s="42"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="G218" s="41"/>
+      <x:c r="H218" s="42"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="G219" s="41"/>
+      <x:c r="H219" s="42"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="G220" s="41"/>
+      <x:c r="H220" s="42"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="G221" s="41"/>
+      <x:c r="H221" s="42"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="G222" s="41"/>
+      <x:c r="H222" s="42"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="G223" s="41"/>
+      <x:c r="H223" s="42"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="G224" s="41"/>
+      <x:c r="H224" s="42"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="G225" s="41"/>
+      <x:c r="H225" s="42"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="G226" s="41"/>
+      <x:c r="H226" s="42"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="G227" s="41"/>
+      <x:c r="H227" s="42"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="G228" s="41"/>
+      <x:c r="H228" s="42"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="G229" s="41"/>
+      <x:c r="H229" s="42"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="G230" s="41"/>
+      <x:c r="H230" s="42"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="G231" s="41"/>
+      <x:c r="H231" s="42"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="G232" s="41"/>
+      <x:c r="H232" s="42"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="G233" s="41"/>
+      <x:c r="H233" s="42"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="G234" s="41"/>
+      <x:c r="H234" s="42"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="G235" s="41"/>
+      <x:c r="H235" s="42"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="G236" s="41"/>
+      <x:c r="H236" s="42"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="G237" s="41"/>
+      <x:c r="H237" s="42"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="G238" s="41"/>
+      <x:c r="H238" s="42"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="G239" s="41"/>
+      <x:c r="H239" s="42"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="G240" s="41"/>
+      <x:c r="H240" s="42"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="G241" s="41"/>
+      <x:c r="H241" s="42"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="G242" s="41"/>
+      <x:c r="H242" s="42"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="G243" s="41"/>
+      <x:c r="H243" s="42"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="G244" s="41"/>
+      <x:c r="H244" s="42"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="G245" s="41"/>
+      <x:c r="H245" s="42"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="G246" s="41"/>
+      <x:c r="H246" s="42"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="G247" s="41"/>
+      <x:c r="H247" s="42"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="G248" s="41"/>
+      <x:c r="H248" s="42"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="G249" s="41"/>
+      <x:c r="H249" s="42"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="G250" s="41"/>
+      <x:c r="H250" s="42"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="G251" s="41"/>
+      <x:c r="H251" s="42"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="G252" s="41"/>
+      <x:c r="H252" s="42"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="G253" s="41"/>
+      <x:c r="H253" s="42"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="G254" s="41"/>
+      <x:c r="H254" s="42"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="G255" s="41"/>
+      <x:c r="H255" s="42"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="G256" s="41"/>
+      <x:c r="H256" s="42"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="G257" s="41"/>
+      <x:c r="H257" s="42"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="G258" s="41"/>
+      <x:c r="H258" s="42"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="G259" s="41"/>
+      <x:c r="H259" s="42"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="G260" s="41"/>
+      <x:c r="H260" s="42"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="G261" s="41"/>
+      <x:c r="H261" s="42"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="G262" s="41"/>
+      <x:c r="H262" s="42"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="G263" s="41"/>
+      <x:c r="H263" s="42"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="G264" s="41"/>
+      <x:c r="H264" s="42"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="G265" s="41"/>
+      <x:c r="H265" s="42"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="G266" s="41"/>
+      <x:c r="H266" s="42"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="G267" s="41"/>
+      <x:c r="H267" s="42"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="G268" s="41"/>
+      <x:c r="H268" s="42"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="G269" s="41"/>
+      <x:c r="H269" s="42"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="G270" s="41"/>
+      <x:c r="H270" s="42"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="G271" s="41"/>
+      <x:c r="H271" s="42"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="G272" s="41"/>
+      <x:c r="H272" s="42"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="G273" s="41"/>
+      <x:c r="H273" s="42"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="G274" s="41"/>
+      <x:c r="H274" s="42"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="G275" s="41"/>
+      <x:c r="H275" s="42"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="G276" s="41"/>
+      <x:c r="H276" s="42"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="G277" s="41"/>
+      <x:c r="H277" s="42"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="G278" s="41"/>
+      <x:c r="H278" s="42"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="G279" s="41"/>
+      <x:c r="H279" s="42"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="G280" s="41"/>
+      <x:c r="H280" s="42"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="G281" s="41"/>
+      <x:c r="H281" s="42"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="G282" s="41"/>
+      <x:c r="H282" s="42"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="G283" s="41"/>
+      <x:c r="H283" s="42"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="G284" s="41"/>
+      <x:c r="H284" s="42"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="G285" s="41"/>
+      <x:c r="H285" s="42"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="G286" s="41"/>
+      <x:c r="H286" s="42"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="G287" s="41"/>
+      <x:c r="H287" s="42"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="G288" s="41"/>
+      <x:c r="H288" s="42"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="G289" s="41"/>
+      <x:c r="H289" s="42"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="G290" s="41"/>
+      <x:c r="H290" s="42"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="G291" s="41"/>
+      <x:c r="H291" s="42"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="G292" s="41"/>
+      <x:c r="H292" s="42"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="G293" s="41"/>
+      <x:c r="H293" s="42"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="G294" s="41"/>
+      <x:c r="H294" s="42"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="G295" s="41"/>
+      <x:c r="H295" s="42"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="G296" s="41"/>
+      <x:c r="H296" s="42"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="G297" s="41"/>
+      <x:c r="H297" s="42"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="G298" s="41"/>
+      <x:c r="H298" s="42"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="G299" s="41"/>
+      <x:c r="H299" s="42"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="G300" s="41"/>
+      <x:c r="H300" s="42"/>
+    </x:row>
+    <x:row r="301">
+      <x:c r="G301" s="41"/>
+      <x:c r="H301" s="42"/>
+    </x:row>
+    <x:row r="302">
+      <x:c r="G302" s="41"/>
+      <x:c r="H302" s="42"/>
+    </x:row>
+    <x:row r="303">
+      <x:c r="G303" s="41"/>
+      <x:c r="H303" s="42"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="G304" s="41"/>
+      <x:c r="H304" s="42"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="G305" s="41"/>
+      <x:c r="H305" s="42"/>
+    </x:row>
+    <x:row r="306">
+      <x:c r="G306" s="41"/>
+      <x:c r="H306" s="42"/>
+    </x:row>
+    <x:row r="307">
+      <x:c r="G307" s="41"/>
+      <x:c r="H307" s="42"/>
+    </x:row>
+    <x:row r="308">
+      <x:c r="G308" s="41"/>
+      <x:c r="H308" s="42"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="G309" s="41"/>
+      <x:c r="H309" s="42"/>
+    </x:row>
+    <x:row r="310">
+      <x:c r="G310" s="41"/>
+      <x:c r="H310" s="42"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="G311" s="41"/>
+      <x:c r="H311" s="42"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="G312" s="41"/>
+      <x:c r="H312" s="42"/>
+    </x:row>
+    <x:row r="313">
+      <x:c r="G313" s="41"/>
+      <x:c r="H313" s="42"/>
+    </x:row>
+    <x:row r="314">
+      <x:c r="G314" s="41"/>
+      <x:c r="H314" s="42"/>
+    </x:row>
+    <x:row r="315">
+      <x:c r="G315" s="41"/>
+      <x:c r="H315" s="42"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="G316" s="41"/>
+      <x:c r="H316" s="42"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="G317" s="41"/>
+      <x:c r="H317" s="42"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="G318" s="41"/>
+      <x:c r="H318" s="42"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="G319" s="41"/>
+      <x:c r="H319" s="42"/>
+    </x:row>
+    <x:row r="320">
+      <x:c r="G320" s="41"/>
+      <x:c r="H320" s="42"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="G321" s="41"/>
+      <x:c r="H321" s="42"/>
+    </x:row>
+    <x:row r="322">
+      <x:c r="G322" s="41"/>
+      <x:c r="H322" s="42"/>
+    </x:row>
+    <x:row r="323">
+      <x:c r="G323" s="41"/>
+      <x:c r="H323" s="42"/>
+    </x:row>
+    <x:row r="324">
+      <x:c r="G324" s="41"/>
+      <x:c r="H324" s="42"/>
+    </x:row>
+    <x:row r="325">
+      <x:c r="G325" s="41"/>
+      <x:c r="H325" s="42"/>
+    </x:row>
+    <x:row r="326">
+      <x:c r="G326" s="41"/>
+      <x:c r="H326" s="42"/>
+    </x:row>
+    <x:row r="327">
+      <x:c r="G327" s="41"/>
+      <x:c r="H327" s="42"/>
+    </x:row>
+    <x:row r="328">
+      <x:c r="G328" s="41"/>
+      <x:c r="H328" s="42"/>
+    </x:row>
+    <x:row r="329">
+      <x:c r="G329" s="41"/>
+      <x:c r="H329" s="42"/>
+    </x:row>
+    <x:row r="330">
+      <x:c r="G330" s="41"/>
+      <x:c r="H330" s="42"/>
+    </x:row>
+    <x:row r="331">
+      <x:c r="G331" s="41"/>
+      <x:c r="H331" s="42"/>
+    </x:row>
+    <x:row r="332">
+      <x:c r="G332" s="41"/>
+      <x:c r="H332" s="42"/>
+    </x:row>
+    <x:row r="333">
+      <x:c r="G333" s="41"/>
+      <x:c r="H333" s="42"/>
+    </x:row>
+    <x:row r="334">
+      <x:c r="G334" s="41"/>
+      <x:c r="H334" s="42"/>
+    </x:row>
+    <x:row r="335">
+      <x:c r="G335" s="41"/>
+      <x:c r="H335" s="42"/>
+    </x:row>
+    <x:row r="336">
+      <x:c r="G336" s="41"/>
+      <x:c r="H336" s="42"/>
+    </x:row>
+    <x:row r="337">
+      <x:c r="G337" s="41"/>
+      <x:c r="H337" s="42"/>
+    </x:row>
+    <x:row r="338">
+      <x:c r="G338" s="41"/>
+      <x:c r="H338" s="42"/>
+    </x:row>
+    <x:row r="339">
+      <x:c r="G339" s="41"/>
+      <x:c r="H339" s="42"/>
+    </x:row>
+    <x:row r="340">
+      <x:c r="G340" s="41"/>
+      <x:c r="H340" s="42"/>
+    </x:row>
+    <x:row r="341">
+      <x:c r="G341" s="41"/>
+      <x:c r="H341" s="42"/>
+    </x:row>
+    <x:row r="342">
+      <x:c r="G342" s="41"/>
+      <x:c r="H342" s="42"/>
+    </x:row>
+    <x:row r="343">
+      <x:c r="G343" s="41"/>
+      <x:c r="H343" s="42"/>
+    </x:row>
+    <x:row r="344">
+      <x:c r="G344" s="41"/>
+      <x:c r="H344" s="42"/>
+    </x:row>
+    <x:row r="345">
+      <x:c r="G345" s="41"/>
+      <x:c r="H345" s="42"/>
+    </x:row>
+    <x:row r="346">
+      <x:c r="G346" s="41"/>
+      <x:c r="H346" s="42"/>
+    </x:row>
+    <x:row r="347">
+      <x:c r="G347" s="41"/>
+      <x:c r="H347" s="42"/>
+    </x:row>
+    <x:row r="348">
+      <x:c r="G348" s="41"/>
+      <x:c r="H348" s="42"/>
+    </x:row>
+    <x:row r="349">
+      <x:c r="G349" s="41"/>
+      <x:c r="H349" s="42"/>
+    </x:row>
+    <x:row r="350">
+      <x:c r="G350" s="41"/>
+      <x:c r="H350" s="42"/>
+    </x:row>
+    <x:row r="351">
+      <x:c r="G351" s="41"/>
+      <x:c r="H351" s="42"/>
+    </x:row>
+    <x:row r="352">
+      <x:c r="G352" s="41"/>
+      <x:c r="H352" s="42"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="G353" s="41"/>
+      <x:c r="H353" s="42"/>
+    </x:row>
+    <x:row r="354">
+      <x:c r="G354" s="41"/>
+      <x:c r="H354" s="42"/>
+    </x:row>
+    <x:row r="355">
+      <x:c r="G355" s="41"/>
+      <x:c r="H355" s="42"/>
+    </x:row>
+    <x:row r="356">
+      <x:c r="G356" s="41"/>
+      <x:c r="H356" s="42"/>
+    </x:row>
+    <x:row r="357">
+      <x:c r="G357" s="41"/>
+      <x:c r="H357" s="42"/>
+    </x:row>
+    <x:row r="358">
+      <x:c r="G358" s="41"/>
+      <x:c r="H358" s="42"/>
+    </x:row>
+    <x:row r="359">
+      <x:c r="G359" s="41"/>
+      <x:c r="H359" s="42"/>
+    </x:row>
+    <x:row r="360">
+      <x:c r="G360" s="41"/>
+      <x:c r="H360" s="42"/>
+    </x:row>
+    <x:row r="361">
+      <x:c r="G361" s="41"/>
+      <x:c r="H361" s="42"/>
+    </x:row>
+    <x:row r="362">
+      <x:c r="G362" s="41"/>
+      <x:c r="H362" s="42"/>
+    </x:row>
+    <x:row r="363">
+      <x:c r="G363" s="41"/>
+      <x:c r="H363" s="42"/>
+    </x:row>
+    <x:row r="364">
+      <x:c r="G364" s="41"/>
+      <x:c r="H364" s="42"/>
+    </x:row>
+    <x:row r="365">
+      <x:c r="G365" s="41"/>
+      <x:c r="H365" s="42"/>
+    </x:row>
+    <x:row r="366">
+      <x:c r="G366" s="41"/>
+      <x:c r="H366" s="42"/>
+    </x:row>
+    <x:row r="367">
+      <x:c r="G367" s="41"/>
+      <x:c r="H367" s="42"/>
+    </x:row>
+    <x:row r="368">
+      <x:c r="G368" s="41"/>
+      <x:c r="H368" s="42"/>
+    </x:row>
+    <x:row r="369">
+      <x:c r="G369" s="41"/>
+      <x:c r="H369" s="42"/>
+    </x:row>
+    <x:row r="370">
+      <x:c r="G370" s="41"/>
+      <x:c r="H370" s="42"/>
+    </x:row>
+    <x:row r="371">
+      <x:c r="G371" s="41"/>
+      <x:c r="H371" s="42"/>
+    </x:row>
+    <x:row r="372">
+      <x:c r="G372" s="41"/>
+      <x:c r="H372" s="42"/>
+    </x:row>
+    <x:row r="373">
+      <x:c r="G373" s="41"/>
+      <x:c r="H373" s="42"/>
+    </x:row>
+    <x:row r="374">
+      <x:c r="G374" s="41"/>
+      <x:c r="H374" s="42"/>
+    </x:row>
+    <x:row r="375">
+      <x:c r="G375" s="41"/>
+      <x:c r="H375" s="42"/>
+    </x:row>
+    <x:row r="376">
+      <x:c r="G376" s="41"/>
+      <x:c r="H376" s="42"/>
+    </x:row>
+    <x:row r="377">
+      <x:c r="G377" s="41"/>
+      <x:c r="H377" s="42"/>
+    </x:row>
+    <x:row r="378">
+      <x:c r="G378" s="41"/>
+      <x:c r="H378" s="42"/>
+    </x:row>
+    <x:row r="379">
+      <x:c r="G379" s="41"/>
+      <x:c r="H379" s="42"/>
+    </x:row>
+    <x:row r="380">
+      <x:c r="G380" s="41"/>
+      <x:c r="H380" s="42"/>
+    </x:row>
+    <x:row r="381">
+      <x:c r="G381" s="41"/>
+      <x:c r="H381" s="42"/>
+    </x:row>
+    <x:row r="382">
+      <x:c r="G382" s="41"/>
+      <x:c r="H382" s="42"/>
+    </x:row>
+    <x:row r="383">
+      <x:c r="G383" s="41"/>
+      <x:c r="H383" s="42"/>
+    </x:row>
+    <x:row r="384">
+      <x:c r="G384" s="41"/>
+      <x:c r="H384" s="42"/>
+    </x:row>
+    <x:row r="385">
+      <x:c r="G385" s="41"/>
+      <x:c r="H385" s="42"/>
+    </x:row>
+    <x:row r="386">
+      <x:c r="G386" s="41"/>
+      <x:c r="H386" s="42"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="G387" s="41"/>
+      <x:c r="H387" s="42"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="G388" s="41"/>
+      <x:c r="H388" s="42"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="G389" s="41"/>
+      <x:c r="H389" s="42"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="G390" s="41"/>
+      <x:c r="H390" s="42"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="G391" s="41"/>
+      <x:c r="H391" s="42"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="G392" s="41"/>
+      <x:c r="H392" s="42"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="G393" s="41"/>
+      <x:c r="H393" s="42"/>
+    </x:row>
+    <x:row r="394">
+      <x:c r="G394" s="41"/>
+      <x:c r="H394" s="42"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="G395" s="41"/>
+      <x:c r="H395" s="42"/>
+    </x:row>
+    <x:row r="396">
+      <x:c r="G396" s="41"/>
+      <x:c r="H396" s="42"/>
+    </x:row>
+    <x:row r="397">
+      <x:c r="G397" s="41"/>
+      <x:c r="H397" s="42"/>
+    </x:row>
+    <x:row r="398">
+      <x:c r="G398" s="41"/>
+      <x:c r="H398" s="42"/>
+    </x:row>
+    <x:row r="399">
+      <x:c r="G399" s="41"/>
+      <x:c r="H399" s="42"/>
+    </x:row>
+    <x:row r="400">
+      <x:c r="G400" s="41"/>
+      <x:c r="H400" s="42"/>
+    </x:row>
+    <x:row r="401">
+      <x:c r="G401" s="41"/>
+      <x:c r="H401" s="42"/>
+    </x:row>
+    <x:row r="402">
+      <x:c r="G402" s="41"/>
+      <x:c r="H402" s="42"/>
+    </x:row>
+    <x:row r="403">
+      <x:c r="G403" s="41"/>
+      <x:c r="H403" s="42"/>
+    </x:row>
+    <x:row r="404">
+      <x:c r="G404" s="41"/>
+      <x:c r="H404" s="42"/>
+    </x:row>
+    <x:row r="405">
+      <x:c r="G405" s="41"/>
+      <x:c r="H405" s="42"/>
+    </x:row>
+    <x:row r="406">
+      <x:c r="G406" s="41"/>
+      <x:c r="H406" s="42"/>
+    </x:row>
+    <x:row r="407">
+      <x:c r="G407" s="41"/>
+      <x:c r="H407" s="42"/>
+    </x:row>
+    <x:row r="408">
+      <x:c r="G408" s="41"/>
+      <x:c r="H408" s="42"/>
+    </x:row>
+    <x:row r="409">
+      <x:c r="G409" s="41"/>
+      <x:c r="H409" s="42"/>
+    </x:row>
+    <x:row r="410">
+      <x:c r="G410" s="41"/>
+      <x:c r="H410" s="42"/>
+    </x:row>
+    <x:row r="411">
+      <x:c r="G411" s="41"/>
+      <x:c r="H411" s="42"/>
+    </x:row>
+    <x:row r="412">
+      <x:c r="G412" s="41"/>
+      <x:c r="H412" s="42"/>
+    </x:row>
+    <x:row r="413">
+      <x:c r="G413" s="41"/>
+      <x:c r="H413" s="42"/>
+    </x:row>
+    <x:row r="414">
+      <x:c r="G414" s="41"/>
+      <x:c r="H414" s="42"/>
+    </x:row>
+    <x:row r="415">
+      <x:c r="G415" s="41"/>
+      <x:c r="H415" s="42"/>
+    </x:row>
+    <x:row r="416">
+      <x:c r="G416" s="41"/>
+      <x:c r="H416" s="42"/>
+    </x:row>
+    <x:row r="417">
+      <x:c r="G417" s="41"/>
+      <x:c r="H417" s="42"/>
+    </x:row>
+    <x:row r="418">
+      <x:c r="G418" s="41"/>
+      <x:c r="H418" s="42"/>
+    </x:row>
+    <x:row r="419">
+      <x:c r="G419" s="41"/>
+      <x:c r="H419" s="42"/>
+    </x:row>
+    <x:row r="420">
+      <x:c r="G420" s="41"/>
+      <x:c r="H420" s="42"/>
+    </x:row>
+    <x:row r="421">
+      <x:c r="G421" s="41"/>
+      <x:c r="H421" s="42"/>
+    </x:row>
+    <x:row r="422">
+      <x:c r="G422" s="41"/>
+      <x:c r="H422" s="42"/>
+    </x:row>
+    <x:row r="423">
+      <x:c r="G423" s="41"/>
+      <x:c r="H423" s="42"/>
+    </x:row>
+    <x:row r="424">
+      <x:c r="G424" s="41"/>
+      <x:c r="H424" s="42"/>
+    </x:row>
+    <x:row r="425">
+      <x:c r="G425" s="41"/>
+      <x:c r="H425" s="42"/>
+    </x:row>
+    <x:row r="426">
+      <x:c r="G426" s="41"/>
+      <x:c r="H426" s="42"/>
+    </x:row>
+    <x:row r="427">
+      <x:c r="G427" s="41"/>
+      <x:c r="H427" s="42"/>
+    </x:row>
+    <x:row r="428">
+      <x:c r="G428" s="41"/>
+      <x:c r="H428" s="42"/>
+    </x:row>
+    <x:row r="429">
+      <x:c r="G429" s="41"/>
+      <x:c r="H429" s="42"/>
+    </x:row>
+    <x:row r="430">
+      <x:c r="G430" s="41"/>
+      <x:c r="H430" s="42"/>
+    </x:row>
+    <x:row r="431">
+      <x:c r="G431" s="41"/>
+      <x:c r="H431" s="42"/>
+    </x:row>
+    <x:row r="432">
+      <x:c r="G432" s="41"/>
+      <x:c r="H432" s="42"/>
+    </x:row>
+    <x:row r="433">
+      <x:c r="G433" s="41"/>
+      <x:c r="H433" s="42"/>
+    </x:row>
+    <x:row r="434">
+      <x:c r="G434" s="41"/>
+      <x:c r="H434" s="42"/>
+    </x:row>
+    <x:row r="435">
+      <x:c r="G435" s="41"/>
+      <x:c r="H435" s="42"/>
+    </x:row>
+    <x:row r="436">
+      <x:c r="G436" s="41"/>
+      <x:c r="H436" s="42"/>
+    </x:row>
+    <x:row r="437">
+      <x:c r="G437" s="41"/>
+      <x:c r="H437" s="42"/>
+    </x:row>
+    <x:row r="438">
+      <x:c r="G438" s="41"/>
+      <x:c r="H438" s="42"/>
+    </x:row>
+    <x:row r="439">
+      <x:c r="G439" s="41"/>
+      <x:c r="H439" s="42"/>
+    </x:row>
+    <x:row r="440">
+      <x:c r="G440" s="41"/>
+      <x:c r="H440" s="42"/>
+    </x:row>
+    <x:row r="441">
+      <x:c r="G441" s="41"/>
+      <x:c r="H441" s="42"/>
+    </x:row>
+    <x:row r="442">
+      <x:c r="G442" s="41"/>
+      <x:c r="H442" s="42"/>
+    </x:row>
+    <x:row r="443">
+      <x:c r="G443" s="41"/>
+      <x:c r="H443" s="42"/>
+    </x:row>
+    <x:row r="444">
+      <x:c r="G444" s="41"/>
+      <x:c r="H444" s="42"/>
+    </x:row>
+    <x:row r="445">
+      <x:c r="G445" s="41"/>
+      <x:c r="H445" s="42"/>
+    </x:row>
+    <x:row r="446">
+      <x:c r="G446" s="41"/>
+      <x:c r="H446" s="42"/>
+    </x:row>
+    <x:row r="447">
+      <x:c r="G447" s="41"/>
+      <x:c r="H447" s="42"/>
+    </x:row>
+    <x:row r="448">
+      <x:c r="G448" s="41"/>
+      <x:c r="H448" s="42"/>
+    </x:row>
+    <x:row r="449">
+      <x:c r="G449" s="41"/>
+      <x:c r="H449" s="42"/>
+    </x:row>
+    <x:row r="450">
+      <x:c r="G450" s="41"/>
+      <x:c r="H450" s="42"/>
+    </x:row>
+    <x:row r="451">
+      <x:c r="G451" s="41"/>
+      <x:c r="H451" s="42"/>
+    </x:row>
+    <x:row r="452">
+      <x:c r="G452" s="41"/>
+      <x:c r="H452" s="42"/>
+    </x:row>
+    <x:row r="453">
+      <x:c r="G453" s="41"/>
+      <x:c r="H453" s="42"/>
+    </x:row>
+    <x:row r="454">
+      <x:c r="G454" s="41"/>
+      <x:c r="H454" s="42"/>
+    </x:row>
+    <x:row r="455">
+      <x:c r="G455" s="41"/>
+      <x:c r="H455" s="42"/>
+    </x:row>
+    <x:row r="456">
+      <x:c r="G456" s="41"/>
+      <x:c r="H456" s="42"/>
+    </x:row>
+    <x:row r="457">
+      <x:c r="G457" s="41"/>
+      <x:c r="H457" s="42"/>
+    </x:row>
+    <x:row r="458">
+      <x:c r="G458" s="41"/>
+      <x:c r="H458" s="42"/>
+    </x:row>
+    <x:row r="459">
+      <x:c r="G459" s="41"/>
+      <x:c r="H459" s="42"/>
+    </x:row>
+    <x:row r="460">
+      <x:c r="G460" s="41"/>
+      <x:c r="H460" s="42"/>
+    </x:row>
+    <x:row r="461">
+      <x:c r="G461" s="41"/>
+      <x:c r="H461" s="42"/>
+    </x:row>
+    <x:row r="462">
+      <x:c r="G462" s="41"/>
+      <x:c r="H462" s="42"/>
+    </x:row>
+    <x:row r="463">
+      <x:c r="G463" s="41"/>
+      <x:c r="H463" s="42"/>
+    </x:row>
+    <x:row r="464">
+      <x:c r="G464" s="41"/>
+      <x:c r="H464" s="42"/>
+    </x:row>
+    <x:row r="465">
+      <x:c r="G465" s="41"/>
+      <x:c r="H465" s="42"/>
+    </x:row>
+    <x:row r="466">
+      <x:c r="G466" s="41"/>
+      <x:c r="H466" s="42"/>
+    </x:row>
+    <x:row r="467">
+      <x:c r="G467" s="41"/>
+      <x:c r="H467" s="42"/>
+    </x:row>
+    <x:row r="468">
+      <x:c r="G468" s="41"/>
+      <x:c r="H468" s="42"/>
+    </x:row>
+    <x:row r="469">
+      <x:c r="G469" s="41"/>
+      <x:c r="H469" s="42"/>
+    </x:row>
+    <x:row r="470">
+      <x:c r="G470" s="41"/>
+      <x:c r="H470" s="42"/>
+    </x:row>
+    <x:row r="471">
+      <x:c r="G471" s="41"/>
+      <x:c r="H471" s="42"/>
+    </x:row>
+    <x:row r="472">
+      <x:c r="G472" s="41"/>
+      <x:c r="H472" s="42"/>
+    </x:row>
+    <x:row r="473">
+      <x:c r="G473" s="41"/>
+      <x:c r="H473" s="42"/>
+    </x:row>
+    <x:row r="474">
+      <x:c r="G474" s="41"/>
+      <x:c r="H474" s="42"/>
+    </x:row>
+    <x:row r="475">
+      <x:c r="G475" s="41"/>
+      <x:c r="H475" s="42"/>
+    </x:row>
+    <x:row r="476">
+      <x:c r="G476" s="41"/>
+      <x:c r="H476" s="42"/>
+    </x:row>
+    <x:row r="477">
+      <x:c r="G477" s="41"/>
+      <x:c r="H477" s="42"/>
+    </x:row>
+    <x:row r="478">
+      <x:c r="G478" s="41"/>
+      <x:c r="H478" s="42"/>
+    </x:row>
+    <x:row r="479">
+      <x:c r="G479" s="41"/>
+      <x:c r="H479" s="42"/>
+    </x:row>
+    <x:row r="480">
+      <x:c r="G480" s="41"/>
+      <x:c r="H480" s="42"/>
+    </x:row>
+    <x:row r="481">
+      <x:c r="G481" s="41"/>
+      <x:c r="H481" s="42"/>
+    </x:row>
+    <x:row r="482">
+      <x:c r="G482" s="41"/>
+      <x:c r="H482" s="42"/>
+    </x:row>
+    <x:row r="483">
+      <x:c r="G483" s="41"/>
+      <x:c r="H483" s="42"/>
+    </x:row>
+    <x:row r="484">
+      <x:c r="G484" s="41"/>
+      <x:c r="H484" s="42"/>
+    </x:row>
+    <x:row r="485">
+      <x:c r="G485" s="41"/>
+      <x:c r="H485" s="42"/>
+    </x:row>
+    <x:row r="486">
+      <x:c r="G486" s="41"/>
+      <x:c r="H486" s="42"/>
+    </x:row>
+    <x:row r="487">
+      <x:c r="G487" s="41"/>
+      <x:c r="H487" s="42"/>
+    </x:row>
+    <x:row r="488">
+      <x:c r="G488" s="41"/>
+      <x:c r="H488" s="42"/>
+    </x:row>
+    <x:row r="489">
+      <x:c r="G489" s="41"/>
+      <x:c r="H489" s="42"/>
+    </x:row>
+    <x:row r="490">
+      <x:c r="G490" s="41"/>
+      <x:c r="H490" s="42"/>
+    </x:row>
+    <x:row r="491">
+      <x:c r="G491" s="41"/>
+      <x:c r="H491" s="42"/>
+    </x:row>
+    <x:row r="492">
+      <x:c r="G492" s="41"/>
+      <x:c r="H492" s="42"/>
+    </x:row>
+    <x:row r="493">
+      <x:c r="G493" s="41"/>
+      <x:c r="H493" s="42"/>
+    </x:row>
+    <x:row r="494">
+      <x:c r="G494" s="41"/>
+      <x:c r="H494" s="42"/>
+    </x:row>
+    <x:row r="495">
+      <x:c r="G495" s="41"/>
+      <x:c r="H495" s="42"/>
+    </x:row>
+    <x:row r="496">
+      <x:c r="G496" s="41"/>
+      <x:c r="H496" s="42"/>
+    </x:row>
+    <x:row r="497">
+      <x:c r="G497" s="41"/>
+      <x:c r="H497" s="42"/>
+    </x:row>
+    <x:row r="498">
+      <x:c r="G498" s="41"/>
+      <x:c r="H498" s="42"/>
+    </x:row>
+    <x:row r="499">
+      <x:c r="G499" s="41"/>
+      <x:c r="H499" s="42"/>
+    </x:row>
+    <x:row r="500">
+      <x:c r="G500" s="41"/>
+      <x:c r="H500" s="42"/>
+    </x:row>
+    <x:row r="501">
+      <x:c r="G501" s="41"/>
+      <x:c r="H501" s="42"/>
+    </x:row>
+    <x:row r="502">
+      <x:c r="G502" s="41"/>
+      <x:c r="H502" s="42"/>
+    </x:row>
+    <x:row r="503">
+      <x:c r="G503" s="41"/>
+      <x:c r="H503" s="42"/>
+    </x:row>
+    <x:row r="504">
+      <x:c r="G504" s="41"/>
+      <x:c r="H504" s="42"/>
+    </x:row>
+    <x:row r="505">
+      <x:c r="G505" s="41"/>
+      <x:c r="H505" s="42"/>
+    </x:row>
+    <x:row r="506">
+      <x:c r="G506" s="41"/>
+      <x:c r="H506" s="42"/>
+    </x:row>
+    <x:row r="507">
+      <x:c r="G507" s="41"/>
+      <x:c r="H507" s="42"/>
+    </x:row>
+    <x:row r="508">
+      <x:c r="G508" s="41"/>
+      <x:c r="H508" s="42"/>
+    </x:row>
+    <x:row r="509">
+      <x:c r="G509" s="41"/>
+      <x:c r="H509" s="42"/>
+    </x:row>
+    <x:row r="510">
+      <x:c r="G510" s="41"/>
+      <x:c r="H510" s="42"/>
+    </x:row>
+    <x:row r="511">
+      <x:c r="G511" s="41"/>
+      <x:c r="H511" s="42"/>
+    </x:row>
+    <x:row r="512">
+      <x:c r="G512" s="41"/>
+      <x:c r="H512" s="42"/>
+    </x:row>
+    <x:row r="513">
+      <x:c r="G513" s="41"/>
+      <x:c r="H513" s="42"/>
+    </x:row>
+    <x:row r="514">
+      <x:c r="G514" s="41"/>
+      <x:c r="H514" s="42"/>
+    </x:row>
+    <x:row r="515">
+      <x:c r="G515" s="41"/>
+      <x:c r="H515" s="42"/>
+    </x:row>
+    <x:row r="516">
+      <x:c r="G516" s="41"/>
+      <x:c r="H516" s="42"/>
+    </x:row>
+    <x:row r="517">
+      <x:c r="G517" s="41"/>
+      <x:c r="H517" s="42"/>
+    </x:row>
+    <x:row r="518">
+      <x:c r="G518" s="41"/>
+      <x:c r="H518" s="42"/>
+    </x:row>
+    <x:row r="519">
+      <x:c r="G519" s="41"/>
+      <x:c r="H519" s="42"/>
+    </x:row>
+    <x:row r="520">
+      <x:c r="G520" s="41"/>
+      <x:c r="H520" s="42"/>
+    </x:row>
+    <x:row r="521">
+      <x:c r="G521" s="41"/>
+      <x:c r="H521" s="42"/>
+    </x:row>
+    <x:row r="522">
+      <x:c r="G522" s="41"/>
+      <x:c r="H522" s="42"/>
+    </x:row>
+    <x:row r="523">
+      <x:c r="G523" s="41"/>
+      <x:c r="H523" s="42"/>
+    </x:row>
+    <x:row r="524">
+      <x:c r="G524" s="41"/>
+      <x:c r="H524" s="42"/>
+    </x:row>
+    <x:row r="525">
+      <x:c r="G525" s="41"/>
+      <x:c r="H525" s="42"/>
+    </x:row>
+    <x:row r="526">
+      <x:c r="G526" s="41"/>
+      <x:c r="H526" s="42"/>
+    </x:row>
+    <x:row r="527">
+      <x:c r="G527" s="41"/>
+      <x:c r="H527" s="42"/>
+    </x:row>
+    <x:row r="528">
+      <x:c r="G528" s="41"/>
+      <x:c r="H528" s="42"/>
+    </x:row>
+    <x:row r="529">
+      <x:c r="G529" s="41"/>
+      <x:c r="H529" s="42"/>
+    </x:row>
+    <x:row r="530">
+      <x:c r="G530" s="41"/>
+      <x:c r="H530" s="42"/>
+    </x:row>
+    <x:row r="531">
+      <x:c r="G531" s="41"/>
+      <x:c r="H531" s="42"/>
+    </x:row>
+    <x:row r="532">
+      <x:c r="G532" s="41"/>
+      <x:c r="H532" s="42"/>
+    </x:row>
+    <x:row r="533">
+      <x:c r="G533" s="41"/>
+      <x:c r="H533" s="42"/>
+    </x:row>
+    <x:row r="534">
+      <x:c r="G534" s="41"/>
+      <x:c r="H534" s="42"/>
+    </x:row>
+    <x:row r="535">
+      <x:c r="G535" s="41"/>
+      <x:c r="H535" s="42"/>
+    </x:row>
+    <x:row r="536">
+      <x:c r="G536" s="41"/>
+      <x:c r="H536" s="42"/>
+    </x:row>
+    <x:row r="537">
+      <x:c r="G537" s="41"/>
+      <x:c r="H537" s="42"/>
+    </x:row>
+    <x:row r="538">
+      <x:c r="G538" s="41"/>
+      <x:c r="H538" s="42"/>
+    </x:row>
+    <x:row r="539">
+      <x:c r="G539" s="41"/>
+      <x:c r="H539" s="42"/>
+    </x:row>
+    <x:row r="540">
+      <x:c r="G540" s="41"/>
+      <x:c r="H540" s="42"/>
+    </x:row>
+    <x:row r="541">
+      <x:c r="G541" s="41"/>
+      <x:c r="H541" s="42"/>
+    </x:row>
+    <x:row r="542">
+      <x:c r="G542" s="41"/>
+      <x:c r="H542" s="42"/>
+    </x:row>
+    <x:row r="543">
+      <x:c r="G543" s="41"/>
+      <x:c r="H543" s="42"/>
+    </x:row>
+    <x:row r="544">
+      <x:c r="G544" s="41"/>
+      <x:c r="H544" s="42"/>
+    </x:row>
+    <x:row r="545">
+      <x:c r="G545" s="41"/>
+      <x:c r="H545" s="42"/>
+    </x:row>
+    <x:row r="546">
+      <x:c r="G546" s="41"/>
+      <x:c r="H546" s="42"/>
+    </x:row>
+    <x:row r="547">
+      <x:c r="G547" s="41"/>
+      <x:c r="H547" s="42"/>
+    </x:row>
+    <x:row r="548">
+      <x:c r="G548" s="41"/>
+      <x:c r="H548" s="42"/>
+    </x:row>
+    <x:row r="549">
+      <x:c r="G549" s="41"/>
+      <x:c r="H549" s="42"/>
+    </x:row>
+    <x:row r="550">
+      <x:c r="G550" s="41"/>
+      <x:c r="H550" s="42"/>
+    </x:row>
+    <x:row r="551">
+      <x:c r="G551" s="41"/>
+      <x:c r="H551" s="42"/>
+    </x:row>
+    <x:row r="552">
+      <x:c r="G552" s="41"/>
+      <x:c r="H552" s="42"/>
+    </x:row>
+    <x:row r="553">
+      <x:c r="G553" s="41"/>
+      <x:c r="H553" s="42"/>
+    </x:row>
+    <x:row r="554">
+      <x:c r="G554" s="41"/>
+      <x:c r="H554" s="42"/>
+    </x:row>
+    <x:row r="555">
+      <x:c r="G555" s="41"/>
+      <x:c r="H555" s="42"/>
+    </x:row>
+    <x:row r="556">
+      <x:c r="G556" s="41"/>
+      <x:c r="H556" s="42"/>
+    </x:row>
+    <x:row r="557">
+      <x:c r="G557" s="41"/>
+      <x:c r="H557" s="42"/>
+    </x:row>
+    <x:row r="558">
+      <x:c r="G558" s="41"/>
+      <x:c r="H558" s="42"/>
+    </x:row>
+    <x:row r="559">
+      <x:c r="G559" s="41"/>
+      <x:c r="H559" s="42"/>
+    </x:row>
+    <x:row r="560">
+      <x:c r="G560" s="41"/>
+      <x:c r="H560" s="42"/>
+    </x:row>
+    <x:row r="561">
+      <x:c r="G561" s="41"/>
+      <x:c r="H561" s="42"/>
+    </x:row>
+    <x:row r="562">
+      <x:c r="G562" s="41"/>
+      <x:c r="H562" s="42"/>
+    </x:row>
+    <x:row r="563">
+      <x:c r="G563" s="41"/>
+      <x:c r="H563" s="42"/>
+    </x:row>
+    <x:row r="564">
+      <x:c r="G564" s="41"/>
+      <x:c r="H564" s="42"/>
+    </x:row>
+    <x:row r="565">
+      <x:c r="G565" s="41"/>
+      <x:c r="H565" s="42"/>
+    </x:row>
+    <x:row r="566">
+      <x:c r="G566" s="41"/>
+      <x:c r="H566" s="42"/>
+    </x:row>
+    <x:row r="567">
+      <x:c r="G567" s="41"/>
+      <x:c r="H567" s="42"/>
+    </x:row>
+    <x:row r="568">
+      <x:c r="G568" s="41"/>
+      <x:c r="H568" s="42"/>
+    </x:row>
+    <x:row r="569">
+      <x:c r="G569" s="41"/>
+      <x:c r="H569" s="42"/>
+    </x:row>
+    <x:row r="570">
+      <x:c r="G570" s="41"/>
+      <x:c r="H570" s="42"/>
+    </x:row>
+    <x:row r="571">
+      <x:c r="G571" s="41"/>
+      <x:c r="H571" s="42"/>
+    </x:row>
+    <x:row r="572">
+      <x:c r="G572" s="41"/>
+      <x:c r="H572" s="42"/>
+    </x:row>
+    <x:row r="573">
+      <x:c r="G573" s="41"/>
+      <x:c r="H573" s="42"/>
+    </x:row>
+    <x:row r="574">
+      <x:c r="G574" s="41"/>
+      <x:c r="H574" s="42"/>
+    </x:row>
+    <x:row r="575">
+      <x:c r="G575" s="41"/>
+      <x:c r="H575" s="42"/>
+    </x:row>
+    <x:row r="576">
+      <x:c r="G576" s="41"/>
+      <x:c r="H576" s="42"/>
+    </x:row>
+    <x:row r="577">
+      <x:c r="G577" s="41"/>
+      <x:c r="H577" s="42"/>
+    </x:row>
+    <x:row r="578">
+      <x:c r="G578" s="41"/>
+      <x:c r="H578" s="42"/>
+    </x:row>
+    <x:row r="579">
+      <x:c r="G579" s="41"/>
+      <x:c r="H579" s="42"/>
+    </x:row>
+    <x:row r="580">
+      <x:c r="G580" s="41"/>
+      <x:c r="H580" s="42"/>
+    </x:row>
+    <x:row r="581">
+      <x:c r="G581" s="41"/>
+      <x:c r="H581" s="42"/>
+    </x:row>
+    <x:row r="582">
+      <x:c r="G582" s="41"/>
+      <x:c r="H582" s="42"/>
+    </x:row>
+    <x:row r="583">
+      <x:c r="G583" s="41"/>
+      <x:c r="H583" s="42"/>
+    </x:row>
+    <x:row r="584">
+      <x:c r="G584" s="41"/>
+      <x:c r="H584" s="42"/>
+    </x:row>
+    <x:row r="585">
+      <x:c r="G585" s="41"/>
+      <x:c r="H585" s="42"/>
+    </x:row>
+    <x:row r="586">
+      <x:c r="G586" s="41"/>
+      <x:c r="H586" s="42"/>
+    </x:row>
+    <x:row r="587">
+      <x:c r="G587" s="41"/>
+      <x:c r="H587" s="42"/>
+    </x:row>
+    <x:row r="588">
+      <x:c r="G588" s="41"/>
+      <x:c r="H588" s="42"/>
+    </x:row>
+    <x:row r="589">
+      <x:c r="G589" s="41"/>
+      <x:c r="H589" s="42"/>
+    </x:row>
+    <x:row r="590">
+      <x:c r="G590" s="41"/>
+      <x:c r="H590" s="42"/>
+    </x:row>
+    <x:row r="591">
+      <x:c r="G591" s="41"/>
+      <x:c r="H591" s="42"/>
+    </x:row>
+    <x:row r="592">
+      <x:c r="G592" s="41"/>
+      <x:c r="H592" s="42"/>
+    </x:row>
+    <x:row r="593">
+      <x:c r="G593" s="41"/>
+      <x:c r="H593" s="42"/>
+    </x:row>
+    <x:row r="594">
+      <x:c r="G594" s="41"/>
+      <x:c r="H594" s="42"/>
+    </x:row>
+    <x:row r="595">
+      <x:c r="G595" s="41"/>
+      <x:c r="H595" s="42"/>
+    </x:row>
+    <x:row r="596">
+      <x:c r="G596" s="41"/>
+      <x:c r="H596" s="42"/>
+    </x:row>
+    <x:row r="597">
+      <x:c r="G597" s="41"/>
+      <x:c r="H597" s="42"/>
+    </x:row>
+    <x:row r="598">
+      <x:c r="G598" s="41"/>
+      <x:c r="H598" s="42"/>
+    </x:row>
+    <x:row r="599">
+      <x:c r="G599" s="41"/>
+      <x:c r="H599" s="42"/>
+    </x:row>
+    <x:row r="600">
+      <x:c r="G600" s="41"/>
+      <x:c r="H600" s="42"/>
+    </x:row>
+    <x:row r="601">
+      <x:c r="G601" s="41"/>
+      <x:c r="H601" s="42"/>
+    </x:row>
+    <x:row r="602">
+      <x:c r="G602" s="41"/>
+      <x:c r="H602" s="42"/>
+    </x:row>
+    <x:row r="603">
+      <x:c r="G603" s="41"/>
+      <x:c r="H603" s="42"/>
+    </x:row>
+    <x:row r="604">
+      <x:c r="G604" s="41"/>
+      <x:c r="H604" s="42"/>
+    </x:row>
+    <x:row r="605">
+      <x:c r="G605" s="41"/>
+      <x:c r="H605" s="42"/>
+    </x:row>
+    <x:row r="606">
+      <x:c r="G606" s="41"/>
+      <x:c r="H606" s="42"/>
+    </x:row>
+    <x:row r="607">
+      <x:c r="G607" s="41"/>
+      <x:c r="H607" s="42"/>
+    </x:row>
+    <x:row r="608">
+      <x:c r="G608" s="41"/>
+      <x:c r="H608" s="42"/>
+    </x:row>
+    <x:row r="609">
+      <x:c r="G609" s="41"/>
+      <x:c r="H609" s="42"/>
+    </x:row>
+    <x:row r="610">
+      <x:c r="G610" s="41"/>
+      <x:c r="H610" s="42"/>
+    </x:row>
+    <x:row r="611">
+      <x:c r="G611" s="41"/>
+      <x:c r="H611" s="42"/>
+    </x:row>
+    <x:row r="612">
+      <x:c r="G612" s="41"/>
+      <x:c r="H612" s="42"/>
+    </x:row>
+    <x:row r="613">
+      <x:c r="G613" s="41"/>
+      <x:c r="H613" s="42"/>
+    </x:row>
+    <x:row r="614">
+      <x:c r="G614" s="41"/>
+      <x:c r="H614" s="42"/>
+    </x:row>
+    <x:row r="615">
+      <x:c r="G615" s="41"/>
+      <x:c r="H615" s="42"/>
+    </x:row>
+    <x:row r="616">
+      <x:c r="G616" s="41"/>
+      <x:c r="H616" s="42"/>
+    </x:row>
+    <x:row r="617">
+      <x:c r="G617" s="41"/>
+      <x:c r="H617" s="42"/>
+    </x:row>
+    <x:row r="618">
+      <x:c r="G618" s="41"/>
+      <x:c r="H618" s="42"/>
+    </x:row>
+    <x:row r="619">
+      <x:c r="G619" s="41"/>
+      <x:c r="H619" s="42"/>
+    </x:row>
+    <x:row r="620">
+      <x:c r="G620" s="41"/>
+      <x:c r="H620" s="42"/>
+    </x:row>
+    <x:row r="621">
+      <x:c r="G621" s="41"/>
+      <x:c r="H621" s="42"/>
+    </x:row>
+    <x:row r="622">
+      <x:c r="G622" s="41"/>
+      <x:c r="H622" s="42"/>
+    </x:row>
+    <x:row r="623">
+      <x:c r="G623" s="41"/>
+      <x:c r="H623" s="42"/>
+    </x:row>
+    <x:row r="624">
+      <x:c r="G624" s="41"/>
+      <x:c r="H624" s="42"/>
+    </x:row>
+    <x:row r="625">
+      <x:c r="G625" s="41"/>
+      <x:c r="H625" s="42"/>
+    </x:row>
+    <x:row r="626">
+      <x:c r="G626" s="41"/>
+      <x:c r="H626" s="42"/>
+    </x:row>
+    <x:row r="627">
+      <x:c r="G627" s="41"/>
+      <x:c r="H627" s="42"/>
+    </x:row>
+    <x:row r="628">
+      <x:c r="G628" s="41"/>
+      <x:c r="H628" s="42"/>
+    </x:row>
+    <x:row r="629">
+      <x:c r="G629" s="41"/>
+      <x:c r="H629" s="42"/>
+    </x:row>
+    <x:row r="630">
+      <x:c r="G630" s="41"/>
+      <x:c r="H630" s="42"/>
+    </x:row>
+    <x:row r="631">
+      <x:c r="G631" s="41"/>
+      <x:c r="H631" s="42"/>
+    </x:row>
+    <x:row r="632">
+      <x:c r="G632" s="41"/>
+      <x:c r="H632" s="42"/>
+    </x:row>
+    <x:row r="633">
+      <x:c r="G633" s="41"/>
+      <x:c r="H633" s="42"/>
+    </x:row>
+    <x:row r="634">
+      <x:c r="G634" s="41"/>
+      <x:c r="H634" s="42"/>
+    </x:row>
+    <x:row r="635">
+      <x:c r="G635" s="41"/>
+      <x:c r="H635" s="42"/>
+    </x:row>
+    <x:row r="636">
+      <x:c r="G636" s="41"/>
+      <x:c r="H636" s="42"/>
+    </x:row>
+    <x:row r="637">
+      <x:c r="G637" s="41"/>
+      <x:c r="H637" s="42"/>
+    </x:row>
+    <x:row r="638">
+      <x:c r="G638" s="41"/>
+      <x:c r="H638" s="42"/>
+    </x:row>
+    <x:row r="639">
+      <x:c r="G639" s="41"/>
+      <x:c r="H639" s="42"/>
+    </x:row>
+    <x:row r="640">
+      <x:c r="G640" s="41"/>
+      <x:c r="H640" s="42"/>
+    </x:row>
+    <x:row r="641">
+      <x:c r="G641" s="41"/>
+      <x:c r="H641" s="42"/>
+    </x:row>
+    <x:row r="642">
+      <x:c r="G642" s="41"/>
+      <x:c r="H642" s="42"/>
+    </x:row>
+    <x:row r="643">
+      <x:c r="G643" s="41"/>
+      <x:c r="H643" s="42"/>
+    </x:row>
+    <x:row r="644">
+      <x:c r="G644" s="41"/>
+      <x:c r="H644" s="42"/>
+    </x:row>
+    <x:row r="645">
+      <x:c r="G645" s="41"/>
+      <x:c r="H645" s="42"/>
+    </x:row>
+    <x:row r="646">
+      <x:c r="G646" s="41"/>
+      <x:c r="H646" s="42"/>
+    </x:row>
+    <x:row r="647">
+      <x:c r="G647" s="41"/>
+      <x:c r="H647" s="42"/>
+    </x:row>
+    <x:row r="648">
+      <x:c r="G648" s="41"/>
+      <x:c r="H648" s="42"/>
+    </x:row>
+    <x:row r="649">
+      <x:c r="G649" s="41"/>
+      <x:c r="H649" s="42"/>
+    </x:row>
+    <x:row r="650">
+      <x:c r="G650" s="41"/>
+      <x:c r="H650" s="42"/>
+    </x:row>
+    <x:row r="651">
+      <x:c r="G651" s="41"/>
+      <x:c r="H651" s="42"/>
+    </x:row>
+    <x:row r="652">
+      <x:c r="G652" s="41"/>
+      <x:c r="H652" s="42"/>
+    </x:row>
+    <x:row r="653">
+      <x:c r="G653" s="41"/>
+      <x:c r="H653" s="42"/>
+    </x:row>
+    <x:row r="654">
+      <x:c r="G654" s="41"/>
+      <x:c r="H654" s="42"/>
+    </x:row>
+    <x:row r="655">
+      <x:c r="G655" s="41"/>
+      <x:c r="H655" s="42"/>
+    </x:row>
+    <x:row r="656">
+      <x:c r="G656" s="41"/>
+      <x:c r="H656" s="42"/>
+    </x:row>
+    <x:row r="657">
+      <x:c r="G657" s="41"/>
+      <x:c r="H657" s="42"/>
+    </x:row>
+    <x:row r="658">
+      <x:c r="G658" s="41"/>
+      <x:c r="H658" s="42"/>
+    </x:row>
+    <x:row r="659">
+      <x:c r="G659" s="41"/>
+      <x:c r="H659" s="42"/>
+    </x:row>
+    <x:row r="660">
+      <x:c r="G660" s="41"/>
+      <x:c r="H660" s="42"/>
+    </x:row>
+    <x:row r="661">
+      <x:c r="G661" s="41"/>
+      <x:c r="H661" s="42"/>
+    </x:row>
+    <x:row r="662">
+      <x:c r="G662" s="41"/>
+      <x:c r="H662" s="42"/>
+    </x:row>
+    <x:row r="663">
+      <x:c r="G663" s="41"/>
+      <x:c r="H663" s="42"/>
+    </x:row>
+    <x:row r="664">
+      <x:c r="G664" s="41"/>
+      <x:c r="H664" s="42"/>
+    </x:row>
+    <x:row r="665">
+      <x:c r="G665" s="41"/>
+      <x:c r="H665" s="42"/>
+    </x:row>
+    <x:row r="666">
+      <x:c r="G666" s="41"/>
+      <x:c r="H666" s="42"/>
+    </x:row>
+    <x:row r="667">
+      <x:c r="G667" s="41"/>
+      <x:c r="H667" s="42"/>
+    </x:row>
+    <x:row r="668">
+      <x:c r="G668" s="41"/>
+      <x:c r="H668" s="42"/>
+    </x:row>
+    <x:row r="669">
+      <x:c r="G669" s="41"/>
+      <x:c r="H669" s="42"/>
+    </x:row>
+    <x:row r="670">
+      <x:c r="G670" s="41"/>
+      <x:c r="H670" s="42"/>
+    </x:row>
+    <x:row r="671">
+      <x:c r="G671" s="41"/>
+      <x:c r="H671" s="42"/>
+    </x:row>
+    <x:row r="672">
+      <x:c r="G672" s="41"/>
+      <x:c r="H672" s="42"/>
+    </x:row>
+    <x:row r="673">
+      <x:c r="G673" s="41"/>
+      <x:c r="H673" s="42"/>
+    </x:row>
+    <x:row r="674">
+      <x:c r="G674" s="41"/>
+      <x:c r="H674" s="42"/>
+    </x:row>
+    <x:row r="675">
+      <x:c r="G675" s="41"/>
+      <x:c r="H675" s="42"/>
+    </x:row>
+    <x:row r="676">
+      <x:c r="G676" s="41"/>
+      <x:c r="H676" s="42"/>
+    </x:row>
+    <x:row r="677">
+      <x:c r="G677" s="41"/>
+      <x:c r="H677" s="42"/>
+    </x:row>
+    <x:row r="678">
+      <x:c r="G678" s="41"/>
+      <x:c r="H678" s="42"/>
+    </x:row>
+    <x:row r="679">
+      <x:c r="G679" s="41"/>
+      <x:c r="H679" s="42"/>
+    </x:row>
+    <x:row r="680">
+      <x:c r="G680" s="41"/>
+      <x:c r="H680" s="42"/>
+    </x:row>
+    <x:row r="681">
+      <x:c r="G681" s="41"/>
+      <x:c r="H681" s="42"/>
+    </x:row>
+    <x:row r="682">
+      <x:c r="G682" s="41"/>
+      <x:c r="H682" s="42"/>
+    </x:row>
+    <x:row r="683">
+      <x:c r="G683" s="41"/>
+      <x:c r="H683" s="42"/>
+    </x:row>
+    <x:row r="684">
+      <x:c r="G684" s="41"/>
+      <x:c r="H684" s="42"/>
+    </x:row>
+    <x:row r="685">
+      <x:c r="G685" s="41"/>
+      <x:c r="H685" s="42"/>
+    </x:row>
+    <x:row r="686">
+      <x:c r="G686" s="41"/>
+      <x:c r="H686" s="42"/>
+    </x:row>
+    <x:row r="687">
+      <x:c r="G687" s="41"/>
+      <x:c r="H687" s="42"/>
+    </x:row>
+    <x:row r="688">
+      <x:c r="G688" s="41"/>
+      <x:c r="H688" s="42"/>
+    </x:row>
+    <x:row r="689">
+      <x:c r="G689" s="41"/>
+      <x:c r="H689" s="42"/>
+    </x:row>
+    <x:row r="690">
+      <x:c r="G690" s="41"/>
+      <x:c r="H690" s="42"/>
+    </x:row>
+    <x:row r="691">
+      <x:c r="G691" s="41"/>
+      <x:c r="H691" s="42"/>
+    </x:row>
+    <x:row r="692">
+      <x:c r="G692" s="41"/>
+      <x:c r="H692" s="42"/>
+    </x:row>
+    <x:row r="693">
+      <x:c r="G693" s="41"/>
+      <x:c r="H693" s="42"/>
+    </x:row>
+    <x:row r="694">
+      <x:c r="G694" s="41"/>
+      <x:c r="H694" s="42"/>
+    </x:row>
+    <x:row r="695">
+      <x:c r="G695" s="41"/>
+      <x:c r="H695" s="42"/>
+    </x:row>
+    <x:row r="696">
+      <x:c r="G696" s="41"/>
+      <x:c r="H696" s="42"/>
+    </x:row>
+    <x:row r="697">
+      <x:c r="G697" s="41"/>
+      <x:c r="H697" s="42"/>
+    </x:row>
+    <x:row r="698">
+      <x:c r="G698" s="41"/>
+      <x:c r="H698" s="42"/>
+    </x:row>
+    <x:row r="699">
+      <x:c r="G699" s="41"/>
+      <x:c r="H699" s="42"/>
+    </x:row>
+    <x:row r="700">
+      <x:c r="G700" s="41"/>
+      <x:c r="H700" s="42"/>
+    </x:row>
+    <x:row r="701">
+      <x:c r="G701" s="41"/>
+      <x:c r="H701" s="42"/>
+    </x:row>
+    <x:row r="702">
+      <x:c r="G702" s="41"/>
+      <x:c r="H702" s="42"/>
+    </x:row>
+    <x:row r="703">
+      <x:c r="G703" s="41"/>
+      <x:c r="H703" s="42"/>
+    </x:row>
+    <x:row r="704">
+      <x:c r="G704" s="41"/>
+      <x:c r="H704" s="42"/>
+    </x:row>
+    <x:row r="705">
+      <x:c r="G705" s="41"/>
+      <x:c r="H705" s="42"/>
+    </x:row>
+    <x:row r="706">
+      <x:c r="G706" s="41"/>
+      <x:c r="H706" s="42"/>
+    </x:row>
+    <x:row r="707">
+      <x:c r="G707" s="41"/>
+      <x:c r="H707" s="42"/>
+    </x:row>
+    <x:row r="708">
+      <x:c r="G708" s="41"/>
+      <x:c r="H708" s="42"/>
+    </x:row>
+    <x:row r="709">
+      <x:c r="G709" s="41"/>
+      <x:c r="H709" s="42"/>
+    </x:row>
+    <x:row r="710">
+      <x:c r="G710" s="41"/>
+      <x:c r="H710" s="42"/>
+    </x:row>
+    <x:row r="711">
+      <x:c r="G711" s="41"/>
+      <x:c r="H711" s="42"/>
+    </x:row>
+    <x:row r="712">
+      <x:c r="G712" s="41"/>
+      <x:c r="H712" s="42"/>
+    </x:row>
+    <x:row r="713">
+      <x:c r="G713" s="41"/>
+      <x:c r="H713" s="42"/>
+    </x:row>
+    <x:row r="714">
+      <x:c r="G714" s="41"/>
+      <x:c r="H714" s="42"/>
+    </x:row>
+    <x:row r="715">
+      <x:c r="G715" s="41"/>
+      <x:c r="H715" s="42"/>
+    </x:row>
+    <x:row r="716">
+      <x:c r="G716" s="41"/>
+      <x:c r="H716" s="42"/>
+    </x:row>
+    <x:row r="717">
+      <x:c r="G717" s="41"/>
+      <x:c r="H717" s="42"/>
+    </x:row>
+    <x:row r="718">
+      <x:c r="G718" s="41"/>
+      <x:c r="H718" s="42"/>
+    </x:row>
+    <x:row r="719">
+      <x:c r="G719" s="41"/>
+      <x:c r="H719" s="42"/>
+    </x:row>
+    <x:row r="720">
+      <x:c r="G720" s="41"/>
+      <x:c r="H720" s="42"/>
+    </x:row>
+    <x:row r="721">
+      <x:c r="G721" s="41"/>
+      <x:c r="H721" s="42"/>
+    </x:row>
+    <x:row r="722">
+      <x:c r="G722" s="41"/>
+      <x:c r="H722" s="42"/>
+    </x:row>
+    <x:row r="723">
+      <x:c r="G723" s="41"/>
+      <x:c r="H723" s="42"/>
+    </x:row>
+    <x:row r="724">
+      <x:c r="G724" s="41"/>
+      <x:c r="H724" s="42"/>
+    </x:row>
+    <x:row r="725">
+      <x:c r="G725" s="41"/>
+      <x:c r="H725" s="42"/>
+    </x:row>
+    <x:row r="726">
+      <x:c r="G726" s="41"/>
+      <x:c r="H726" s="42"/>
+    </x:row>
+    <x:row r="727">
+      <x:c r="G727" s="41"/>
+      <x:c r="H727" s="42"/>
+    </x:row>
+    <x:row r="728">
+      <x:c r="G728" s="41"/>
+      <x:c r="H728" s="42"/>
+    </x:row>
+    <x:row r="729">
+      <x:c r="G729" s="41"/>
+      <x:c r="H729" s="42"/>
+    </x:row>
+    <x:row r="730">
+      <x:c r="G730" s="41"/>
+      <x:c r="H730" s="42"/>
+    </x:row>
+    <x:row r="731">
+      <x:c r="G731" s="41"/>
+      <x:c r="H731" s="42"/>
+    </x:row>
+    <x:row r="732">
+      <x:c r="G732" s="41"/>
+      <x:c r="H732" s="42"/>
+    </x:row>
+    <x:row r="733">
+      <x:c r="G733" s="41"/>
+      <x:c r="H733" s="42"/>
+    </x:row>
+    <x:row r="734">
+      <x:c r="G734" s="41"/>
+      <x:c r="H734" s="42"/>
+    </x:row>
+    <x:row r="735">
+      <x:c r="G735" s="41"/>
+      <x:c r="H735" s="42"/>
+    </x:row>
+    <x:row r="736">
+      <x:c r="G736" s="41"/>
+      <x:c r="H736" s="42"/>
+    </x:row>
+    <x:row r="737">
+      <x:c r="G737" s="41"/>
+      <x:c r="H737" s="42"/>
+    </x:row>
+    <x:row r="738">
+      <x:c r="G738" s="41"/>
+      <x:c r="H738" s="42"/>
+    </x:row>
+    <x:row r="739">
+      <x:c r="G739" s="41"/>
+      <x:c r="H739" s="42"/>
+    </x:row>
+    <x:row r="740">
+      <x:c r="G740" s="41"/>
+      <x:c r="H740" s="42"/>
+    </x:row>
+    <x:row r="741">
+      <x:c r="G741" s="41"/>
+      <x:c r="H741" s="42"/>
+    </x:row>
+    <x:row r="742">
+      <x:c r="G742" s="41"/>
+      <x:c r="H742" s="42"/>
+    </x:row>
+    <x:row r="743">
+      <x:c r="G743" s="41"/>
+      <x:c r="H743" s="42"/>
+    </x:row>
+    <x:row r="744">
+      <x:c r="G744" s="41"/>
+      <x:c r="H744" s="42"/>
+    </x:row>
+    <x:row r="745">
+      <x:c r="G745" s="41"/>
+      <x:c r="H745" s="42"/>
+    </x:row>
+    <x:row r="746">
+      <x:c r="G746" s="41"/>
+      <x:c r="H746" s="42"/>
+    </x:row>
+    <x:row r="747">
+      <x:c r="G747" s="41"/>
+      <x:c r="H747" s="42"/>
+    </x:row>
+    <x:row r="748">
+      <x:c r="G748" s="41"/>
+      <x:c r="H748" s="42"/>
+    </x:row>
+    <x:row r="749">
+      <x:c r="G749" s="41"/>
+      <x:c r="H749" s="42"/>
+    </x:row>
+    <x:row r="750">
+      <x:c r="G750" s="41"/>
+      <x:c r="H750" s="42"/>
+    </x:row>
+    <x:row r="751">
+      <x:c r="G751" s="41"/>
+      <x:c r="H751" s="42"/>
+    </x:row>
+    <x:row r="752">
+      <x:c r="G752" s="41"/>
+      <x:c r="H752" s="42"/>
+    </x:row>
+    <x:row r="753">
+      <x:c r="G753" s="41"/>
+      <x:c r="H753" s="42"/>
+    </x:row>
+    <x:row r="754">
+      <x:c r="G754" s="41"/>
+      <x:c r="H754" s="42"/>
+    </x:row>
+    <x:row r="755">
+      <x:c r="G755" s="41"/>
+      <x:c r="H755" s="42"/>
+    </x:row>
+    <x:row r="756">
+      <x:c r="G756" s="41"/>
+      <x:c r="H756" s="42"/>
+    </x:row>
+    <x:row r="757">
+      <x:c r="G757" s="41"/>
+      <x:c r="H757" s="42"/>
+    </x:row>
+    <x:row r="758">
+      <x:c r="G758" s="41"/>
+      <x:c r="H758" s="42"/>
+    </x:row>
+    <x:row r="759">
+      <x:c r="G759" s="41"/>
+      <x:c r="H759" s="42"/>
+    </x:row>
+    <x:row r="760">
+      <x:c r="G760" s="41"/>
+      <x:c r="H760" s="42"/>
+    </x:row>
+    <x:row r="761">
+      <x:c r="G761" s="41"/>
+      <x:c r="H761" s="42"/>
+    </x:row>
+    <x:row r="762">
+      <x:c r="G762" s="41"/>
+      <x:c r="H762" s="42"/>
+    </x:row>
+    <x:row r="763">
+      <x:c r="G763" s="41"/>
+      <x:c r="H763" s="42"/>
+    </x:row>
+    <x:row r="764">
+      <x:c r="G764" s="41"/>
+      <x:c r="H764" s="42"/>
+    </x:row>
+    <x:row r="765">
+      <x:c r="G765" s="41"/>
+      <x:c r="H765" s="42"/>
+    </x:row>
+    <x:row r="766">
+      <x:c r="G766" s="41"/>
+      <x:c r="H766" s="42"/>
+    </x:row>
+    <x:row r="767">
+      <x:c r="G767" s="41"/>
+      <x:c r="H767" s="42"/>
+    </x:row>
+    <x:row r="768">
+      <x:c r="G768" s="41"/>
+      <x:c r="H768" s="42"/>
+    </x:row>
+    <x:row r="769">
+      <x:c r="G769" s="41"/>
+      <x:c r="H769" s="42"/>
+    </x:row>
+    <x:row r="770">
+      <x:c r="G770" s="41"/>
+      <x:c r="H770" s="42"/>
+    </x:row>
+    <x:row r="771">
+      <x:c r="G771" s="41"/>
+      <x:c r="H771" s="42"/>
+    </x:row>
+    <x:row r="772">
+      <x:c r="G772" s="41"/>
+      <x:c r="H772" s="42"/>
+    </x:row>
+    <x:row r="773">
+      <x:c r="G773" s="41"/>
+      <x:c r="H773" s="42"/>
+    </x:row>
+    <x:row r="774">
+      <x:c r="G774" s="41"/>
+      <x:c r="H774" s="42"/>
+    </x:row>
+    <x:row r="775">
+      <x:c r="G775" s="41"/>
+      <x:c r="H775" s="42"/>
+    </x:row>
+    <x:row r="776">
+      <x:c r="G776" s="41"/>
+      <x:c r="H776" s="42"/>
+    </x:row>
+    <x:row r="777">
+      <x:c r="G777" s="41"/>
+      <x:c r="H777" s="42"/>
+    </x:row>
+    <x:row r="778">
+      <x:c r="G778" s="41"/>
+      <x:c r="H778" s="42"/>
+    </x:row>
+    <x:row r="779">
+      <x:c r="G779" s="41"/>
+      <x:c r="H779" s="42"/>
+    </x:row>
+    <x:row r="780">
+      <x:c r="G780" s="41"/>
+      <x:c r="H780" s="42"/>
+    </x:row>
+    <x:row r="781">
+      <x:c r="G781" s="41"/>
+      <x:c r="H781" s="42"/>
+    </x:row>
+    <x:row r="782">
+      <x:c r="G782" s="41"/>
+      <x:c r="H782" s="42"/>
+    </x:row>
+    <x:row r="783">
+      <x:c r="G783" s="41"/>
+      <x:c r="H783" s="42"/>
+    </x:row>
+    <x:row r="784">
+      <x:c r="G784" s="41"/>
+      <x:c r="H784" s="42"/>
+    </x:row>
+    <x:row r="785">
+      <x:c r="G785" s="41"/>
+      <x:c r="H785" s="42"/>
+    </x:row>
+    <x:row r="786">
+      <x:c r="G786" s="41"/>
+      <x:c r="H786" s="42"/>
+    </x:row>
+    <x:row r="787">
+      <x:c r="G787" s="41"/>
+      <x:c r="H787" s="42"/>
+    </x:row>
+    <x:row r="788">
+      <x:c r="G788" s="41"/>
+      <x:c r="H788" s="42"/>
+    </x:row>
+    <x:row r="789">
+      <x:c r="G789" s="41"/>
+      <x:c r="H789" s="42"/>
+    </x:row>
+    <x:row r="790">
+      <x:c r="G790" s="41"/>
+      <x:c r="H790" s="42"/>
+    </x:row>
+    <x:row r="791">
+      <x:c r="G791" s="41"/>
+      <x:c r="H791" s="42"/>
+    </x:row>
+    <x:row r="792">
+      <x:c r="G792" s="41"/>
+      <x:c r="H792" s="42"/>
+    </x:row>
+    <x:row r="793">
+      <x:c r="G793" s="41"/>
+      <x:c r="H793" s="42"/>
+    </x:row>
+    <x:row r="794">
+      <x:c r="G794" s="41"/>
+      <x:c r="H794" s="42"/>
+    </x:row>
+    <x:row r="795">
+      <x:c r="G795" s="41"/>
+      <x:c r="H795" s="42"/>
+    </x:row>
+    <x:row r="796">
+      <x:c r="G796" s="41"/>
+      <x:c r="H796" s="42"/>
+    </x:row>
+    <x:row r="797">
+      <x:c r="G797" s="41"/>
+      <x:c r="H797" s="42"/>
+    </x:row>
+    <x:row r="798">
+      <x:c r="G798" s="41"/>
+      <x:c r="H798" s="42"/>
+    </x:row>
+    <x:row r="799">
+      <x:c r="G799" s="41"/>
+      <x:c r="H799" s="42"/>
+    </x:row>
+    <x:row r="800">
+      <x:c r="G800" s="41"/>
+      <x:c r="H800" s="42"/>
+    </x:row>
+    <x:row r="801">
+      <x:c r="G801" s="41"/>
+      <x:c r="H801" s="42"/>
+    </x:row>
+    <x:row r="802">
+      <x:c r="G802" s="41"/>
+      <x:c r="H802" s="42"/>
+    </x:row>
+    <x:row r="803">
+      <x:c r="G803" s="41"/>
+      <x:c r="H803" s="42"/>
+    </x:row>
+    <x:row r="804">
+      <x:c r="G804" s="41"/>
+      <x:c r="H804" s="42"/>
+    </x:row>
+    <x:row r="805">
+      <x:c r="G805" s="41"/>
+      <x:c r="H805" s="42"/>
+    </x:row>
+    <x:row r="806">
+      <x:c r="G806" s="41"/>
+      <x:c r="H806" s="42"/>
+    </x:row>
+    <x:row r="807">
+      <x:c r="G807" s="41"/>
+      <x:c r="H807" s="42"/>
+    </x:row>
+    <x:row r="808">
+      <x:c r="G808" s="41"/>
+      <x:c r="H808" s="42"/>
+    </x:row>
+    <x:row r="809">
+      <x:c r="G809" s="41"/>
+      <x:c r="H809" s="42"/>
+    </x:row>
+    <x:row r="810">
+      <x:c r="G810" s="41"/>
+      <x:c r="H810" s="42"/>
+    </x:row>
+    <x:row r="811">
+      <x:c r="G811" s="41"/>
+      <x:c r="H811" s="42"/>
+    </x:row>
+    <x:row r="812">
+      <x:c r="G812" s="41"/>
+      <x:c r="H812" s="42"/>
+    </x:row>
+    <x:row r="813">
+      <x:c r="G813" s="41"/>
+      <x:c r="H813" s="42"/>
+    </x:row>
+    <x:row r="814">
+      <x:c r="G814" s="41"/>
+      <x:c r="H814" s="42"/>
+    </x:row>
+    <x:row r="815">
+      <x:c r="G815" s="41"/>
+      <x:c r="H815" s="42"/>
+    </x:row>
+    <x:row r="816">
+      <x:c r="G816" s="41"/>
+      <x:c r="H816" s="42"/>
+    </x:row>
+    <x:row r="817">
+      <x:c r="G817" s="41"/>
+      <x:c r="H817" s="42"/>
+    </x:row>
+    <x:row r="818">
+      <x:c r="G818" s="41"/>
+      <x:c r="H818" s="42"/>
+    </x:row>
+    <x:row r="819">
+      <x:c r="G819" s="41"/>
+      <x:c r="H819" s="42"/>
+    </x:row>
+    <x:row r="820">
+      <x:c r="G820" s="41"/>
+      <x:c r="H820" s="42"/>
+    </x:row>
+    <x:row r="821">
+      <x:c r="G821" s="41"/>
+      <x:c r="H821" s="42"/>
+    </x:row>
+    <x:row r="822">
+      <x:c r="G822" s="41"/>
+      <x:c r="H822" s="42"/>
+    </x:row>
+    <x:row r="823">
+      <x:c r="G823" s="41"/>
+      <x:c r="H823" s="42"/>
+    </x:row>
+    <x:row r="824">
+      <x:c r="G824" s="41"/>
+      <x:c r="H824" s="42"/>
+    </x:row>
+    <x:row r="825">
+      <x:c r="G825" s="41"/>
+      <x:c r="H825" s="42"/>
+    </x:row>
+    <x:row r="826">
+      <x:c r="G826" s="41"/>
+      <x:c r="H826" s="42"/>
+    </x:row>
+    <x:row r="827">
+      <x:c r="G827" s="41"/>
+      <x:c r="H827" s="42"/>
+    </x:row>
+    <x:row r="828">
+      <x:c r="G828" s="41"/>
+      <x:c r="H828" s="42"/>
+    </x:row>
+    <x:row r="829">
+      <x:c r="G829" s="41"/>
+      <x:c r="H829" s="42"/>
+    </x:row>
+    <x:row r="830">
+      <x:c r="G830" s="41"/>
+      <x:c r="H830" s="42"/>
+    </x:row>
+    <x:row r="831">
+      <x:c r="G831" s="41"/>
+      <x:c r="H831" s="42"/>
+    </x:row>
+    <x:row r="832">
+      <x:c r="G832" s="41"/>
+      <x:c r="H832" s="42"/>
+    </x:row>
+    <x:row r="833">
+      <x:c r="G833" s="41"/>
+      <x:c r="H833" s="42"/>
+    </x:row>
+    <x:row r="834">
+      <x:c r="G834" s="41"/>
+      <x:c r="H834" s="42"/>
+    </x:row>
+    <x:row r="835">
+      <x:c r="G835" s="41"/>
+      <x:c r="H835" s="42"/>
+    </x:row>
+    <x:row r="836">
+      <x:c r="G836" s="41"/>
+      <x:c r="H836" s="42"/>
+    </x:row>
+    <x:row r="837">
+      <x:c r="G837" s="41"/>
+      <x:c r="H837" s="42"/>
+    </x:row>
+    <x:row r="838">
+      <x:c r="G838" s="41"/>
+      <x:c r="H838" s="42"/>
+    </x:row>
+    <x:row r="839">
+      <x:c r="G839" s="41"/>
+      <x:c r="H839" s="42"/>
+    </x:row>
+    <x:row r="840">
+      <x:c r="G840" s="41"/>
+      <x:c r="H840" s="42"/>
+    </x:row>
+    <x:row r="841">
+      <x:c r="G841" s="41"/>
+      <x:c r="H841" s="42"/>
+    </x:row>
+    <x:row r="842">
+      <x:c r="G842" s="41"/>
+      <x:c r="H842" s="42"/>
+    </x:row>
+    <x:row r="843">
+      <x:c r="G843" s="41"/>
+      <x:c r="H843" s="42"/>
+    </x:row>
+    <x:row r="844">
+      <x:c r="G844" s="41"/>
+      <x:c r="H844" s="42"/>
+    </x:row>
+    <x:row r="845">
+      <x:c r="G845" s="41"/>
+      <x:c r="H845" s="42"/>
+    </x:row>
+    <x:row r="846">
+      <x:c r="G846" s="41"/>
+      <x:c r="H846" s="42"/>
+    </x:row>
+    <x:row r="847">
+      <x:c r="G847" s="41"/>
+      <x:c r="H847" s="42"/>
+    </x:row>
+    <x:row r="848">
+      <x:c r="G848" s="41"/>
+      <x:c r="H848" s="42"/>
+    </x:row>
+    <x:row r="849">
+      <x:c r="G849" s="41"/>
+      <x:c r="H849" s="42"/>
+    </x:row>
+    <x:row r="850">
+      <x:c r="G850" s="41"/>
+      <x:c r="H850" s="42"/>
+    </x:row>
+    <x:row r="851">
+      <x:c r="G851" s="41"/>
+      <x:c r="H851" s="42"/>
+    </x:row>
+    <x:row r="852">
+      <x:c r="G852" s="41"/>
+      <x:c r="H852" s="42"/>
+    </x:row>
+    <x:row r="853">
+      <x:c r="G853" s="41"/>
+      <x:c r="H853" s="42"/>
+    </x:row>
+    <x:row r="854">
+      <x:c r="G854" s="41"/>
+      <x:c r="H854" s="42"/>
+    </x:row>
+    <x:row r="855">
+      <x:c r="G855" s="41"/>
+      <x:c r="H855" s="42"/>
+    </x:row>
+    <x:row r="856">
+      <x:c r="G856" s="41"/>
+      <x:c r="H856" s="42"/>
+    </x:row>
+    <x:row r="857">
+      <x:c r="G857" s="41"/>
+      <x:c r="H857" s="42"/>
+    </x:row>
+    <x:row r="858">
+      <x:c r="G858" s="41"/>
+      <x:c r="H858" s="42"/>
+    </x:row>
+    <x:row r="859">
+      <x:c r="G859" s="41"/>
+      <x:c r="H859" s="42"/>
+    </x:row>
+    <x:row r="860">
+      <x:c r="G860" s="41"/>
+      <x:c r="H860" s="42"/>
+    </x:row>
+    <x:row r="861">
+      <x:c r="G861" s="41"/>
+      <x:c r="H861" s="42"/>
+    </x:row>
+    <x:row r="862">
+      <x:c r="G862" s="41"/>
+      <x:c r="H862" s="42"/>
+    </x:row>
+    <x:row r="863">
+      <x:c r="G863" s="41"/>
+      <x:c r="H863" s="42"/>
+    </x:row>
+    <x:row r="864">
+      <x:c r="G864" s="41"/>
+      <x:c r="H864" s="42"/>
+    </x:row>
+    <x:row r="865">
+      <x:c r="G865" s="41"/>
+      <x:c r="H865" s="42"/>
+    </x:row>
+    <x:row r="866">
+      <x:c r="G866" s="41"/>
+      <x:c r="H866" s="42"/>
+    </x:row>
+    <x:row r="867">
+      <x:c r="G867" s="41"/>
+      <x:c r="H867" s="42"/>
+    </x:row>
+    <x:row r="868">
+      <x:c r="G868" s="41"/>
+      <x:c r="H868" s="42"/>
+    </x:row>
+    <x:row r="869">
+      <x:c r="G869" s="41"/>
+      <x:c r="H869" s="42"/>
+    </x:row>
+    <x:row r="870">
+      <x:c r="G870" s="41"/>
+      <x:c r="H870" s="42"/>
+    </x:row>
+    <x:row r="871">
+      <x:c r="G871" s="41"/>
+      <x:c r="H871" s="42"/>
+    </x:row>
+    <x:row r="872">
+      <x:c r="G872" s="41"/>
+      <x:c r="H872" s="42"/>
+    </x:row>
+    <x:row r="873">
+      <x:c r="G873" s="41"/>
+      <x:c r="H873" s="42"/>
+    </x:row>
+    <x:row r="874">
+      <x:c r="G874" s="41"/>
+      <x:c r="H874" s="42"/>
+    </x:row>
+    <x:row r="875">
+      <x:c r="G875" s="41"/>
+      <x:c r="H875" s="42"/>
+    </x:row>
+    <x:row r="876">
+      <x:c r="G876" s="41"/>
+      <x:c r="H876" s="42"/>
+    </x:row>
+    <x:row r="877">
+      <x:c r="G877" s="41"/>
+      <x:c r="H877" s="42"/>
+    </x:row>
+    <x:row r="878">
+      <x:c r="G878" s="41"/>
+      <x:c r="H878" s="42"/>
+    </x:row>
+    <x:row r="879">
+      <x:c r="G879" s="41"/>
+      <x:c r="H879" s="42"/>
+    </x:row>
+    <x:row r="880">
+      <x:c r="G880" s="41"/>
+      <x:c r="H880" s="42"/>
+    </x:row>
+    <x:row r="881">
+      <x:c r="G881" s="41"/>
+      <x:c r="H881" s="42"/>
+    </x:row>
+    <x:row r="882">
+      <x:c r="G882" s="41"/>
+      <x:c r="H882" s="42"/>
+    </x:row>
+    <x:row r="883">
+      <x:c r="G883" s="41"/>
+      <x:c r="H883" s="42"/>
+    </x:row>
+    <x:row r="884">
+      <x:c r="G884" s="41"/>
+      <x:c r="H884" s="42"/>
+    </x:row>
+    <x:row r="885">
+      <x:c r="G885" s="41"/>
+      <x:c r="H885" s="42"/>
+    </x:row>
+    <x:row r="886">
+      <x:c r="G886" s="41"/>
+      <x:c r="H886" s="42"/>
+    </x:row>
+    <x:row r="887">
+      <x:c r="G887" s="41"/>
+      <x:c r="H887" s="42"/>
+    </x:row>
+    <x:row r="888">
+      <x:c r="G888" s="41"/>
+      <x:c r="H888" s="42"/>
+    </x:row>
+    <x:row r="889">
+      <x:c r="G889" s="41"/>
+      <x:c r="H889" s="42"/>
+    </x:row>
+    <x:row r="890">
+      <x:c r="G890" s="41"/>
+      <x:c r="H890" s="42"/>
+    </x:row>
+    <x:row r="891">
+      <x:c r="G891" s="41"/>
+      <x:c r="H891" s="42"/>
+    </x:row>
+    <x:row r="892">
+      <x:c r="G892" s="41"/>
+      <x:c r="H892" s="42"/>
+    </x:row>
+    <x:row r="893">
+      <x:c r="G893" s="41"/>
+      <x:c r="H893" s="42"/>
+    </x:row>
+    <x:row r="894">
+      <x:c r="G894" s="41"/>
+      <x:c r="H894" s="42"/>
+    </x:row>
+    <x:row r="895">
+      <x:c r="G895" s="41"/>
+      <x:c r="H895" s="42"/>
+    </x:row>
+    <x:row r="896">
+      <x:c r="G896" s="41"/>
+      <x:c r="H896" s="42"/>
+    </x:row>
+    <x:row r="897">
+      <x:c r="G897" s="41"/>
+      <x:c r="H897" s="42"/>
+    </x:row>
+    <x:row r="898">
+      <x:c r="G898" s="41"/>
+      <x:c r="H898" s="42"/>
+    </x:row>
+    <x:row r="899">
+      <x:c r="G899" s="41"/>
+      <x:c r="H899" s="42"/>
+    </x:row>
+    <x:row r="900">
+      <x:c r="G900" s="41"/>
+      <x:c r="H900" s="42"/>
+    </x:row>
+    <x:row r="901">
+      <x:c r="G901" s="41"/>
+      <x:c r="H901" s="42"/>
+    </x:row>
+    <x:row r="902">
+      <x:c r="G902" s="41"/>
+      <x:c r="H902" s="42"/>
+    </x:row>
+    <x:row r="903">
+      <x:c r="G903" s="41"/>
+      <x:c r="H903" s="42"/>
+    </x:row>
+    <x:row r="904">
+      <x:c r="G904" s="41"/>
+      <x:c r="H904" s="42"/>
+    </x:row>
+    <x:row r="905">
+      <x:c r="G905" s="41"/>
+      <x:c r="H905" s="42"/>
+    </x:row>
+    <x:row r="906">
+      <x:c r="G906" s="41"/>
+      <x:c r="H906" s="42"/>
+    </x:row>
+    <x:row r="907">
+      <x:c r="G907" s="41"/>
+      <x:c r="H907" s="42"/>
+    </x:row>
+    <x:row r="908">
+      <x:c r="G908" s="41"/>
+      <x:c r="H908" s="42"/>
+    </x:row>
+    <x:row r="909">
+      <x:c r="G909" s="41"/>
+      <x:c r="H909" s="42"/>
+    </x:row>
+    <x:row r="910">
+      <x:c r="G910" s="41"/>
+      <x:c r="H910" s="42"/>
+    </x:row>
+    <x:row r="911">
+      <x:c r="G911" s="41"/>
+      <x:c r="H911" s="42"/>
+    </x:row>
+    <x:row r="912">
+      <x:c r="G912" s="41"/>
+      <x:c r="H912" s="42"/>
+    </x:row>
+    <x:row r="913">
+      <x:c r="G913" s="41"/>
+      <x:c r="H913" s="42"/>
+    </x:row>
+    <x:row r="914">
+      <x:c r="G914" s="41"/>
+      <x:c r="H914" s="42"/>
+    </x:row>
+    <x:row r="915">
+      <x:c r="G915" s="41"/>
+      <x:c r="H915" s="42"/>
+    </x:row>
+    <x:row r="916">
+      <x:c r="G916" s="41"/>
+      <x:c r="H916" s="42"/>
+    </x:row>
+    <x:row r="917">
+      <x:c r="G917" s="41"/>
+      <x:c r="H917" s="42"/>
+    </x:row>
+    <x:row r="918">
+      <x:c r="G918" s="41"/>
+      <x:c r="H918" s="42"/>
+    </x:row>
+    <x:row r="919">
+      <x:c r="G919" s="41"/>
+      <x:c r="H919" s="42"/>
+    </x:row>
+    <x:row r="920">
+      <x:c r="G920" s="41"/>
+      <x:c r="H920" s="42"/>
+    </x:row>
+    <x:row r="921">
+      <x:c r="G921" s="41"/>
+      <x:c r="H921" s="42"/>
+    </x:row>
+    <x:row r="922">
+      <x:c r="G922" s="41"/>
+      <x:c r="H922" s="42"/>
+    </x:row>
+    <x:row r="923">
+      <x:c r="G923" s="41"/>
+      <x:c r="H923" s="42"/>
+    </x:row>
+    <x:row r="924">
+      <x:c r="G924" s="41"/>
+      <x:c r="H924" s="42"/>
+    </x:row>
+    <x:row r="925">
+      <x:c r="G925" s="41"/>
+      <x:c r="H925" s="42"/>
+    </x:row>
+    <x:row r="926">
+      <x:c r="G926" s="41"/>
+      <x:c r="H926" s="42"/>
+    </x:row>
+    <x:row r="927">
+      <x:c r="G927" s="41"/>
+      <x:c r="H927" s="42"/>
+    </x:row>
+    <x:row r="928">
+      <x:c r="G928" s="41"/>
+      <x:c r="H928" s="42"/>
+    </x:row>
+    <x:row r="929">
+      <x:c r="G929" s="41"/>
+      <x:c r="H929" s="42"/>
+    </x:row>
+    <x:row r="930">
+      <x:c r="G930" s="41"/>
+      <x:c r="H930" s="42"/>
+    </x:row>
+    <x:row r="931">
+      <x:c r="G931" s="41"/>
+      <x:c r="H931" s="42"/>
+    </x:row>
+    <x:row r="932">
+      <x:c r="G932" s="41"/>
+      <x:c r="H932" s="42"/>
+    </x:row>
+    <x:row r="933">
+      <x:c r="G933" s="41"/>
+      <x:c r="H933" s="42"/>
+    </x:row>
+    <x:row r="934">
+      <x:c r="G934" s="41"/>
+      <x:c r="H934" s="42"/>
+    </x:row>
+    <x:row r="935">
+      <x:c r="G935" s="41"/>
+      <x:c r="H935" s="42"/>
+    </x:row>
+    <x:row r="936">
+      <x:c r="G936" s="41"/>
+      <x:c r="H936" s="42"/>
+    </x:row>
+    <x:row r="937">
+      <x:c r="G937" s="41"/>
+      <x:c r="H937" s="42"/>
+    </x:row>
+    <x:row r="938">
+      <x:c r="G938" s="41"/>
+      <x:c r="H938" s="42"/>
+    </x:row>
+    <x:row r="939">
+      <x:c r="G939" s="41"/>
+      <x:c r="H939" s="42"/>
+    </x:row>
+    <x:row r="940">
+      <x:c r="G940" s="41"/>
+      <x:c r="H940" s="42"/>
+    </x:row>
+    <x:row r="941">
+      <x:c r="G941" s="41"/>
+      <x:c r="H941" s="42"/>
+    </x:row>
+    <x:row r="942">
+      <x:c r="G942" s="41"/>
+      <x:c r="H942" s="42"/>
+    </x:row>
+    <x:row r="943">
+      <x:c r="G943" s="41"/>
+      <x:c r="H943" s="42"/>
+    </x:row>
+    <x:row r="944">
+      <x:c r="G944" s="41"/>
+      <x:c r="H944" s="42"/>
+    </x:row>
+    <x:row r="945">
+      <x:c r="G945" s="41"/>
+      <x:c r="H945" s="42"/>
+    </x:row>
+    <x:row r="946">
+      <x:c r="G946" s="41"/>
+      <x:c r="H946" s="42"/>
+    </x:row>
+    <x:row r="947">
+      <x:c r="G947" s="41"/>
+      <x:c r="H947" s="42"/>
+    </x:row>
+    <x:row r="948">
+      <x:c r="G948" s="41"/>
+      <x:c r="H948" s="42"/>
+    </x:row>
+    <x:row r="949">
+      <x:c r="G949" s="41"/>
+      <x:c r="H949" s="42"/>
+    </x:row>
+    <x:row r="950">
+      <x:c r="G950" s="41"/>
+      <x:c r="H950" s="42"/>
+    </x:row>
+    <x:row r="951">
+      <x:c r="G951" s="41"/>
+      <x:c r="H951" s="42"/>
+    </x:row>
+    <x:row r="952">
+      <x:c r="G952" s="41"/>
+      <x:c r="H952" s="42"/>
+    </x:row>
+    <x:row r="953">
+      <x:c r="G953" s="41"/>
+      <x:c r="H953" s="42"/>
+    </x:row>
+    <x:row r="954">
+      <x:c r="G954" s="41"/>
+      <x:c r="H954" s="42"/>
+    </x:row>
+    <x:row r="955">
+      <x:c r="G955" s="41"/>
+      <x:c r="H955" s="42"/>
+    </x:row>
+    <x:row r="956">
+      <x:c r="G956" s="41"/>
+      <x:c r="H956" s="42"/>
+    </x:row>
+    <x:row r="957">
+      <x:c r="G957" s="41"/>
+      <x:c r="H957" s="42"/>
+    </x:row>
+    <x:row r="958">
+      <x:c r="G958" s="41"/>
+      <x:c r="H958" s="42"/>
+    </x:row>
+    <x:row r="959">
+      <x:c r="G959" s="41"/>
+      <x:c r="H959" s="42"/>
+    </x:row>
+    <x:row r="960">
+      <x:c r="G960" s="41"/>
+      <x:c r="H960" s="42"/>
+    </x:row>
+    <x:row r="961">
+      <x:c r="G961" s="41"/>
+      <x:c r="H961" s="42"/>
+    </x:row>
+    <x:row r="962">
+      <x:c r="G962" s="41"/>
+      <x:c r="H962" s="42"/>
+    </x:row>
+    <x:row r="963">
+      <x:c r="G963" s="41"/>
+      <x:c r="H963" s="42"/>
+    </x:row>
+    <x:row r="964">
+      <x:c r="G964" s="41"/>
+      <x:c r="H964" s="42"/>
+    </x:row>
+    <x:row r="965">
+      <x:c r="G965" s="41"/>
+      <x:c r="H965" s="42"/>
+    </x:row>
+    <x:row r="966">
+      <x:c r="G966" s="41"/>
+      <x:c r="H966" s="42"/>
+    </x:row>
+    <x:row r="967">
+      <x:c r="G967" s="41"/>
+      <x:c r="H967" s="42"/>
+    </x:row>
+    <x:row r="968">
+      <x:c r="G968" s="41"/>
+      <x:c r="H968" s="42"/>
+    </x:row>
+    <x:row r="969">
+      <x:c r="G969" s="41"/>
+      <x:c r="H969" s="42"/>
+    </x:row>
+    <x:row r="970">
+      <x:c r="G970" s="41"/>
+      <x:c r="H970" s="42"/>
+    </x:row>
+    <x:row r="971">
+      <x:c r="G971" s="41"/>
+      <x:c r="H971" s="42"/>
+    </x:row>
+    <x:row r="972">
+      <x:c r="G972" s="41"/>
+      <x:c r="H972" s="42"/>
+    </x:row>
+    <x:row r="973">
+      <x:c r="G973" s="41"/>
+      <x:c r="H973" s="42"/>
+    </x:row>
+    <x:row r="974">
+      <x:c r="G974" s="41"/>
+      <x:c r="H974" s="42"/>
+    </x:row>
+    <x:row r="975">
+      <x:c r="G975" s="41"/>
+      <x:c r="H975" s="42"/>
+    </x:row>
+    <x:row r="976">
+      <x:c r="G976" s="41"/>
+      <x:c r="H976" s="42"/>
+    </x:row>
+    <x:row r="977">
+      <x:c r="G977" s="41"/>
+      <x:c r="H977" s="42"/>
+    </x:row>
+    <x:row r="978">
+      <x:c r="G978" s="41"/>
+      <x:c r="H978" s="42"/>
+    </x:row>
+    <x:row r="979">
+      <x:c r="G979" s="41"/>
+      <x:c r="H979" s="42"/>
+    </x:row>
+    <x:row r="980">
+      <x:c r="G980" s="41"/>
+      <x:c r="H980" s="42"/>
+    </x:row>
+    <x:row r="981">
+      <x:c r="G981" s="41"/>
+      <x:c r="H981" s="42"/>
+    </x:row>
+    <x:row r="982">
+      <x:c r="G982" s="41"/>
+      <x:c r="H982" s="42"/>
+    </x:row>
+    <x:row r="983">
+      <x:c r="G983" s="41"/>
+      <x:c r="H983" s="42"/>
+    </x:row>
+    <x:row r="984">
+      <x:c r="G984" s="41"/>
+      <x:c r="H984" s="42"/>
+    </x:row>
+    <x:row r="985">
+      <x:c r="G985" s="41"/>
+      <x:c r="H985" s="42"/>
+    </x:row>
+    <x:row r="986">
+      <x:c r="G986" s="41"/>
+      <x:c r="H986" s="42"/>
+    </x:row>
+    <x:row r="987">
+      <x:c r="G987" s="41"/>
+      <x:c r="H987" s="42"/>
+    </x:row>
+    <x:row r="988">
+      <x:c r="G988" s="41"/>
+      <x:c r="H988" s="42"/>
+    </x:row>
+    <x:row r="989">
+      <x:c r="G989" s="41"/>
+      <x:c r="H989" s="42"/>
+    </x:row>
+    <x:row r="990">
+      <x:c r="G990" s="41"/>
+      <x:c r="H990" s="42"/>
+    </x:row>
+    <x:row r="991">
+      <x:c r="G991" s="41"/>
+      <x:c r="H991" s="42"/>
+    </x:row>
+    <x:row r="992">
+      <x:c r="G992" s="41"/>
+      <x:c r="H992" s="42"/>
+    </x:row>
+    <x:row r="993">
+      <x:c r="G993" s="41"/>
+      <x:c r="H993" s="42"/>
+    </x:row>
+    <x:row r="994">
+      <x:c r="G994" s="41"/>
+      <x:c r="H994" s="42"/>
+    </x:row>
+    <x:row r="995">
+      <x:c r="G995" s="41"/>
+      <x:c r="H995" s="42"/>
+    </x:row>
+    <x:row r="996">
+      <x:c r="G996" s="41"/>
+      <x:c r="H996" s="42"/>
+    </x:row>
+    <x:row r="997">
+      <x:c r="G997" s="41"/>
+      <x:c r="H997" s="42"/>
+    </x:row>
+    <x:row r="998">
+      <x:c r="G998" s="41"/>
+      <x:c r="H998" s="42"/>
+    </x:row>
+    <x:row r="999">
+      <x:c r="G999" s="41"/>
+      <x:c r="H999" s="42"/>
+    </x:row>
+    <x:row r="1000">
+      <x:c r="G1000" s="41"/>
+      <x:c r="H1000" s="42"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
@@ -3790,7 +7087,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd07478c7d12d49ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d2925c47bc74159"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3890,144 +7187,366 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="10"/>
-      <x:c r="B3" s="10"/>
-      <x:c r="C3" s="10"/>
-      <x:c r="D3" s="10"/>
-      <x:c r="E3" s="10"/>
-      <x:c r="F3" s="10"/>
-      <x:c r="G3" s="10"/>
-      <x:c r="H3" s="40"/>
-      <x:c r="I3" s="38"/>
-      <x:c r="J3" s="10"/>
-      <x:c r="K3" s="10"/>
-      <x:c r="L3" s="10"/>
+      <x:c r="A3" s="10" t="str">
+        <x:v>EMCU8361795</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>260324SP552311</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>pickup_request</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str"/>
+      <x:c r="F3" s="10" t="str">
+        <x:v>empty</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H3" s="40" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="I3" s="38" t="n">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
+        <x:v>EGLV400500499060</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="str">
+        <x:v>SHINING INTERNATIONAL DEVELOPMENT LIMITED</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="str">
+        <x:v>SHINING INTERNATIONAL DEVELOPMENT LIMITED</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="10"/>
-      <x:c r="B4" s="10"/>
-      <x:c r="C4" s="10"/>
-      <x:c r="D4" s="10"/>
-      <x:c r="E4" s="10"/>
-      <x:c r="F4" s="10"/>
-      <x:c r="G4" s="10"/>
-      <x:c r="H4" s="40"/>
-      <x:c r="I4" s="38"/>
-      <x:c r="J4" s="10"/>
-      <x:c r="K4" s="10"/>
-      <x:c r="L4" s="10"/>
+      <x:c r="A4" s="10" t="str">
+        <x:v>EMCU8361795</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>260317SP545549</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>pickup_request</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>A1795572</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H4" s="40" t="n">
+        <x:v>28300</x:v>
+      </x:c>
+      <x:c r="I4" s="38" t="n">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
+        <x:v>400500499060</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
+        <x:v>SHINING INTERNATIONAL DEVELOPMENT LIMITED</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="str">
+        <x:v>SHINING INTERNATIONAL DEVELOPMENT LIMITED</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="10"/>
-      <x:c r="B5" s="10"/>
-      <x:c r="C5" s="10"/>
-      <x:c r="D5" s="10"/>
-      <x:c r="E5" s="10"/>
-      <x:c r="F5" s="10"/>
-      <x:c r="G5" s="10"/>
-      <x:c r="H5" s="40"/>
+      <x:c r="A5" s="10" t="str">
+        <x:v>ONEU7524599</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>260331PA558185</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>truck_dropoff</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="str">
+        <x:v>VN83568AQ</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H5" s="40" t="n">
+        <x:v>26000</x:v>
+      </x:c>
       <x:c r="I5" s="38"/>
-      <x:c r="J5" s="10"/>
-      <x:c r="K5" s="10"/>
-      <x:c r="L5" s="10"/>
+      <x:c r="J5" s="10" t="str">
+        <x:v>DADG02202800</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN VANTAGE LOGISTICS</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN VANTAGE LOGISTICS</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="10"/>
-      <x:c r="B6" s="10"/>
-      <x:c r="C6" s="10"/>
-      <x:c r="D6" s="10"/>
-      <x:c r="E6" s="10"/>
-      <x:c r="F6" s="10"/>
-      <x:c r="G6" s="10"/>
-      <x:c r="H6" s="40"/>
-      <x:c r="I6" s="38"/>
-      <x:c r="J6" s="10"/>
-      <x:c r="K6" s="10"/>
-      <x:c r="L6" s="10"/>
+      <x:c r="A6" s="10" t="str">
+        <x:v>ONEU7524599</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>260310SP539765</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>pickup_request</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="str">
+        <x:v>VN83063AQ</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H6" s="40" t="n">
+        <x:v>32500</x:v>
+      </x:c>
+      <x:c r="I6" s="38" t="n">
+        <x:v>46091</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="str"/>
+      <x:c r="K6" s="10" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ITL LOGISTICS TẠI MIỀN TRUNG</x:v>
+      </x:c>
+      <x:c r="L6" s="10" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ITL LOGISTICS TẠI MIỀN TRUNG</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="10"/>
-      <x:c r="B7" s="10"/>
-      <x:c r="C7" s="10"/>
-      <x:c r="D7" s="10"/>
-      <x:c r="E7" s="10"/>
-      <x:c r="F7" s="10"/>
-      <x:c r="G7" s="10"/>
-      <x:c r="H7" s="40"/>
+      <x:c r="A7" s="10" t="str">
+        <x:v>ONEU7524599</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>260301PA531586</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>truck_dropoff</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="str">
+        <x:v>VN83063AQ</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H7" s="40" t="n">
+        <x:v>32500</x:v>
+      </x:c>
       <x:c r="I7" s="38"/>
-      <x:c r="J7" s="10"/>
-      <x:c r="K7" s="10"/>
-      <x:c r="L7" s="10"/>
+      <x:c r="J7" s="10" t="str">
+        <x:v>DADG02482400</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="10"/>
-      <x:c r="B8" s="10"/>
-      <x:c r="C8" s="10"/>
-      <x:c r="D8" s="10"/>
-      <x:c r="E8" s="10"/>
-      <x:c r="F8" s="10"/>
-      <x:c r="G8" s="10"/>
-      <x:c r="H8" s="40"/>
-      <x:c r="I8" s="38"/>
-      <x:c r="J8" s="10"/>
-      <x:c r="K8" s="10"/>
-      <x:c r="L8" s="10"/>
+      <x:c r="A8" s="10" t="str">
+        <x:v>ONEU7524599</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>260228SP530924</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>pickup_request</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="str"/>
+      <x:c r="F8" s="10" t="str">
+        <x:v>empty</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H8" s="40" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="I8" s="38" t="n">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="str">
+        <x:v>DADG02482400</x:v>
+      </x:c>
+      <x:c r="K8" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
+      <x:c r="L8" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="10"/>
-      <x:c r="B9" s="10"/>
-      <x:c r="C9" s="10"/>
-      <x:c r="D9" s="10"/>
-      <x:c r="E9" s="10"/>
-      <x:c r="F9" s="10"/>
-      <x:c r="G9" s="10"/>
-      <x:c r="H9" s="40"/>
+      <x:c r="A9" s="10" t="str">
+        <x:v>GCXU5261606</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>260331PA558329</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>truck_dropoff</x:v>
+      </x:c>
+      <x:c r="E9" s="10" t="str">
+        <x:v>VN83572AQ</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H9" s="40" t="n">
+        <x:v>9496</x:v>
+      </x:c>
       <x:c r="I9" s="38"/>
-      <x:c r="J9" s="10"/>
-      <x:c r="K9" s="10"/>
-      <x:c r="L9" s="10"/>
+      <x:c r="J9" s="10" t="str">
+        <x:v>DADG02410900</x:v>
+      </x:c>
+      <x:c r="K9" s="10" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẠI LÝ VẬN TẢI SAFI TẠI ĐÀ NẴNG</x:v>
+      </x:c>
+      <x:c r="L9" s="10" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẠI LÝ VẬN TẢI SAFI TẠI ĐÀ NẴNG</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="10"/>
-      <x:c r="B10" s="10"/>
-      <x:c r="C10" s="10"/>
-      <x:c r="D10" s="10"/>
-      <x:c r="E10" s="10"/>
-      <x:c r="F10" s="10"/>
-      <x:c r="G10" s="10"/>
-      <x:c r="H10" s="40"/>
-      <x:c r="I10" s="38"/>
-      <x:c r="J10" s="10"/>
-      <x:c r="K10" s="10"/>
-      <x:c r="L10" s="10"/>
+      <x:c r="A10" s="10" t="str">
+        <x:v>GCXU5261606</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>260310SP539765</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>pickup_request</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="str">
+        <x:v>VN83064AQ</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H10" s="40" t="n">
+        <x:v>32500</x:v>
+      </x:c>
+      <x:c r="I10" s="38" t="n">
+        <x:v>46093</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="str"/>
+      <x:c r="K10" s="10" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ITL LOGISTICS TẠI MIỀN TRUNG</x:v>
+      </x:c>
+      <x:c r="L10" s="10" t="str">
+        <x:v>CHI NHÁNH CÔNG TY CỔ PHẦN ITL LOGISTICS TẠI MIỀN TRUNG</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
-      <x:c r="A11" s="10"/>
-      <x:c r="B11" s="10"/>
-      <x:c r="C11" s="10"/>
-      <x:c r="D11" s="10"/>
-      <x:c r="E11" s="10"/>
-      <x:c r="F11" s="10"/>
-      <x:c r="G11" s="10"/>
-      <x:c r="H11" s="40"/>
+      <x:c r="A11" s="10" t="str">
+        <x:v>GCXU5261606</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>260301PA531586</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>truck_dropoff</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str">
+        <x:v>VN83064AQ</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
+        <x:v>full</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H11" s="40" t="n">
+        <x:v>32500</x:v>
+      </x:c>
       <x:c r="I11" s="38"/>
-      <x:c r="J11" s="10"/>
-      <x:c r="K11" s="10"/>
-      <x:c r="L11" s="10"/>
+      <x:c r="J11" s="10" t="str">
+        <x:v>DADG02482400</x:v>
+      </x:c>
+      <x:c r="K11" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
+      <x:c r="L11" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="10"/>
-      <x:c r="B12" s="10"/>
-      <x:c r="C12" s="10"/>
-      <x:c r="D12" s="10"/>
-      <x:c r="E12" s="10"/>
-      <x:c r="F12" s="10"/>
-      <x:c r="G12" s="10"/>
-      <x:c r="H12" s="40"/>
-      <x:c r="I12" s="38"/>
-      <x:c r="J12" s="10"/>
-      <x:c r="K12" s="10"/>
-      <x:c r="L12" s="10"/>
+      <x:c r="A12" s="10" t="str">
+        <x:v>GCXU5261606</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>40HC</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>260228SP531186</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>pickup_request</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="str"/>
+      <x:c r="F12" s="10" t="str">
+        <x:v>empty</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>general</x:v>
+      </x:c>
+      <x:c r="H12" s="40" t="n">
+        <x:v>3700</x:v>
+      </x:c>
+      <x:c r="I12" s="38" t="n">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="str">
+        <x:v>DADG02482400</x:v>
+      </x:c>
+      <x:c r="K12" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
+      <x:c r="L12" s="10" t="str">
+        <x:v>CÔNG TY CỔ PHẦN ITL FREIGHT MANAGEMENT</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="10"/>
@@ -6678,7 +10197,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61f8edea2b9c4c7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4e9fcbcf8524379"/>
   </x:tableParts>
 </x:worksheet>
 </file>